--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4194,7 +4194,7 @@
       <c r="E61" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="n"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4222,18 +4222,250 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="4" t="inlineStr"/>
-      <c r="P61" s="4" t="inlineStr"/>
-      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="N61" s="3" t="n"/>
+      <c r="O61" s="4" t="n"/>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n"/>
       <c r="R61" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0.9813361519749764</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>1.6839</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>2.4561</v>
+      </c>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="n"/>
+      <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>2.321759527394884</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>1.6794</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>2.4106</v>
+      </c>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="n"/>
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="4" t="n"/>
+      <c r="R63" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>1.702044480481879</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>1.6815</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>2.428500000000001</v>
+      </c>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="n"/>
+      <c r="O64" s="4" t="n"/>
+      <c r="P64" s="4" t="n"/>
+      <c r="Q64" s="4" t="n"/>
+      <c r="R64" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>2.422571817444696</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>1.6887</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>2.3913</v>
+      </c>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr"/>
+      <c r="Q65" s="4" t="inlineStr"/>
+      <c r="R65" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R61"/>
+  <autoFilter ref="A1:R65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4426,7 +4426,7 @@
       <c r="E65" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="n"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4454,18 +4454,76 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N65" s="3" t="inlineStr"/>
-      <c r="O65" s="4" t="inlineStr"/>
-      <c r="P65" s="4" t="inlineStr"/>
-      <c r="Q65" s="4" t="inlineStr"/>
+      <c r="N65" s="3" t="n"/>
+      <c r="O65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="4" t="n"/>
       <c r="R65" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>2.731705374724891</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>1.6988</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>2.3712</v>
+      </c>
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr"/>
+      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="R66" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R65"/>
+  <autoFilter ref="A1:R66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4484,7 +4484,7 @@
       <c r="E66" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="n"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -4512,18 +4512,134 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr"/>
-      <c r="O66" s="4" t="inlineStr"/>
-      <c r="P66" s="4" t="inlineStr"/>
-      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="N66" s="3" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="4" t="n"/>
       <c r="R66" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>3.011699293409031</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>1.6949</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>2.3651</v>
+      </c>
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>3.498566546970938</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>1.6883</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>2.3817</v>
+      </c>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr"/>
+      <c r="Q68" s="4" t="inlineStr"/>
+      <c r="R68" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R66"/>
+  <autoFilter ref="A1:R68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4600,7 +4600,7 @@
       <c r="E68" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="n"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -4628,18 +4628,192 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N68" s="3" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr"/>
-      <c r="P68" s="4" t="inlineStr"/>
-      <c r="Q68" s="4" t="inlineStr"/>
+      <c r="N68" s="3" t="n"/>
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="4" t="n"/>
       <c r="R68" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>3.509969014247649</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>1.6834</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>2.3866</v>
+      </c>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="4" t="n"/>
+      <c r="R69" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>1.981133441445615</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>1.6861</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>2.4439</v>
+      </c>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>1.989821035561223</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>1.6798</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>2.4502</v>
+      </c>
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr"/>
+      <c r="Q71" s="4" t="inlineStr"/>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R68"/>
+  <autoFilter ref="A1:R71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4774,7 +4774,7 @@
       <c r="E71" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="n"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -4802,18 +4802,250 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="4" t="inlineStr"/>
-      <c r="P71" s="4" t="inlineStr"/>
-      <c r="Q71" s="4" t="inlineStr"/>
+      <c r="N71" s="3" t="n"/>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="4" t="n"/>
       <c r="R71" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>2.229091856828447</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>1.6804</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>2.4396</v>
+      </c>
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
+      <c r="Q72" s="4" t="n"/>
+      <c r="R72" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0.9970824163095138</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>1.6798</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>2.4902</v>
+      </c>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="n"/>
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n"/>
+      <c r="R73" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>2.310900034750385</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>1.6815</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>2.428500000000001</v>
+      </c>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="n"/>
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
+      <c r="Q74" s="4" t="n"/>
+      <c r="R74" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>3.45476659330477</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>1.6816</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>2.3884</v>
+      </c>
+      <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr"/>
+      <c r="Q75" s="4" t="inlineStr"/>
+      <c r="R75" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R71"/>
+  <autoFilter ref="A1:R75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5006,7 +5006,7 @@
       <c r="E75" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="n"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -5034,18 +5034,76 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N75" s="3" t="inlineStr"/>
-      <c r="O75" s="4" t="inlineStr"/>
-      <c r="P75" s="4" t="inlineStr"/>
-      <c r="Q75" s="4" t="inlineStr"/>
+      <c r="N75" s="3" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="4" t="n"/>
       <c r="R75" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>2.750528495308702</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>1.6797</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>2.4203</v>
+      </c>
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr"/>
+      <c r="Q76" s="4" t="inlineStr"/>
+      <c r="R76" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R75"/>
+  <autoFilter ref="A1:R76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5064,7 +5064,7 @@
       <c r="E76" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="n"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -5092,18 +5092,76 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr"/>
-      <c r="O76" s="4" t="inlineStr"/>
-      <c r="P76" s="4" t="inlineStr"/>
-      <c r="Q76" s="4" t="inlineStr"/>
+      <c r="N76" s="3" t="n"/>
+      <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="4" t="n"/>
       <c r="R76" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>0.7898470983435768</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>1.6888</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>2.4912</v>
+      </c>
+      <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr"/>
+      <c r="Q77" s="4" t="inlineStr"/>
+      <c r="R77" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R76"/>
+  <autoFilter ref="A1:R77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5122,7 +5122,7 @@
       <c r="E77" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="n"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -5150,18 +5150,76 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" s="4" t="inlineStr"/>
+      <c r="N77" s="3" t="n"/>
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="4" t="n"/>
+      <c r="Q77" s="4" t="n"/>
       <c r="R77" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0.1652452797405335</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>1.6865</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>2.5135</v>
+      </c>
+      <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr"/>
+      <c r="Q78" s="4" t="inlineStr"/>
+      <c r="R78" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R77"/>
+  <autoFilter ref="A1:R78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,13 +493,13 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
@@ -5180,7 +5180,7 @@
       <c r="E78" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="n"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -5208,18 +5208,134 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr"/>
-      <c r="O78" s="4" t="inlineStr"/>
-      <c r="P78" s="4" t="inlineStr"/>
-      <c r="Q78" s="4" t="inlineStr"/>
+      <c r="N78" s="3" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
+      <c r="Q78" s="4" t="n"/>
       <c r="R78" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-0.3876838874087851</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>1.6858</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>2.5342</v>
+      </c>
+      <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n"/>
+      <c r="R79" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-0.9279436464728286</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1.6862</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>2.5638</v>
+      </c>
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="inlineStr"/>
+      <c r="R80" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R78"/>
+  <autoFilter ref="A1:R80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5296,7 +5296,7 @@
       <c r="E80" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="n"/>
       <c r="G80" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -5324,18 +5324,250 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr"/>
-      <c r="P80" s="4" t="inlineStr"/>
-      <c r="Q80" s="4" t="inlineStr"/>
+      <c r="N80" s="3" t="n"/>
+      <c r="O80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="4" t="n"/>
       <c r="R80" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>-1.146762423259584</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>1.682</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>2.578</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="n"/>
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="4" t="n"/>
+      <c r="R81" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>-1.146762423259584</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>1.682</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>2.578</v>
+      </c>
+      <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="n"/>
+      <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
+      <c r="Q82" s="4" t="n"/>
+      <c r="R82" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>0.04090408896095798</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>1.6829</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>2.5271</v>
+      </c>
+      <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="n"/>
+      <c r="O83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
+      <c r="Q83" s="4" t="n"/>
+      <c r="R83" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0.05158259006139421</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>2.5309</v>
+      </c>
+      <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr"/>
+      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="R84" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R80"/>
+  <autoFilter ref="A1:R84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R84"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5528,7 +5528,7 @@
       <c r="E84" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="n"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -5556,18 +5556,250 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N84" s="3" t="inlineStr"/>
-      <c r="O84" s="4" t="inlineStr"/>
-      <c r="P84" s="4" t="inlineStr"/>
-      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="N84" s="3" t="n"/>
+      <c r="O84" s="4" t="n"/>
+      <c r="P84" s="4" t="n"/>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>-0.7436942546044323</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>1.6807</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>2.5593</v>
+      </c>
+      <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="n"/>
+      <c r="O85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
+      <c r="Q85" s="4" t="n"/>
+      <c r="R85" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>-1.008484883586247</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>1.6738</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>2.5762</v>
+      </c>
+      <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="n"/>
+      <c r="O86" s="4" t="n"/>
+      <c r="P86" s="4" t="n"/>
+      <c r="Q86" s="4" t="n"/>
+      <c r="R86" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>-1.547839684929908</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>2.590999999999999</v>
+      </c>
+      <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="n"/>
+      <c r="O87" s="4" t="n"/>
+      <c r="P87" s="4" t="n"/>
+      <c r="Q87" s="4" t="n"/>
+      <c r="R87" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>-1.745663442603962</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>2.613</v>
+      </c>
+      <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr"/>
+      <c r="P88" s="4" t="inlineStr"/>
+      <c r="Q88" s="4" t="inlineStr"/>
+      <c r="R88" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R84"/>
+  <autoFilter ref="A1:R88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:AE102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -514,6 +514,19 @@
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="21" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +557,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>xueqiu_change_percent</t>
+          <t>intraday_change_percent</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -607,8 +620,73 @@
           <t>lixinger_source</t>
         </is>
       </c>
-    </row>
-    <row r="2" hidden="1" outlineLevel="1">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>strategy_version</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>composite_score</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>composite_grade</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>score_lower</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>score_upper</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_score</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>absolute_score</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ratio_score</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_contribution</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>absolute_contribution</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ratio_contribution</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>score_quality</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>confirmation_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" outlineLevel="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>记录日期</t>
@@ -636,7 +714,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>雪球当天涨跌幅(%)</t>
+          <t>当天涨跌幅(%)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -697,6 +775,71 @@
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>理杏仁数据源状态</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>评分策略版本</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>综合分</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>综合等级</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>综合分下界</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>综合分上界</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>历史分位得分</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>绝对股息率得分</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>股债倍数得分</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>历史分位贡献</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>绝对股息率贡献</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>股债倍数贡献</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>评分数据质量</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>连续确认状态</t>
         </is>
       </c>
     </row>
@@ -759,6 +902,19 @@
           <t>理杏仁限流</t>
         </is>
       </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr"/>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+      <c r="AB3" s="5" t="inlineStr"/>
+      <c r="AC3" s="5" t="inlineStr"/>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -819,6 +975,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr"/>
+      <c r="AC4" s="5" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -879,6 +1048,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+      <c r="AB5" s="5" t="inlineStr"/>
+      <c r="AC5" s="5" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -933,6 +1115,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -987,6 +1182,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr"/>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+      <c r="AB7" s="5" t="inlineStr"/>
+      <c r="AC7" s="5" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1041,6 +1249,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr"/>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="5" t="inlineStr"/>
+      <c r="AB8" s="5" t="inlineStr"/>
+      <c r="AC8" s="5" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1095,6 +1316,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="AA9" s="5" t="inlineStr"/>
+      <c r="AB9" s="5" t="inlineStr"/>
+      <c r="AC9" s="5" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1149,6 +1383,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="5" t="inlineStr"/>
+      <c r="AB10" s="5" t="inlineStr"/>
+      <c r="AC10" s="5" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1203,6 +1450,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S11" s="8" t="inlineStr"/>
+      <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="8" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
+      <c r="W11" s="10" t="inlineStr"/>
+      <c r="X11" s="10" t="inlineStr"/>
+      <c r="Y11" s="10" t="inlineStr"/>
+      <c r="Z11" s="10" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr"/>
+      <c r="AB11" s="10" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr"/>
+      <c r="AD11" s="8" t="inlineStr"/>
+      <c r="AE11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1257,6 +1517,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S12" s="8" t="inlineStr"/>
+      <c r="T12" s="10" t="inlineStr"/>
+      <c r="U12" s="8" t="inlineStr"/>
+      <c r="V12" s="10" t="inlineStr"/>
+      <c r="W12" s="10" t="inlineStr"/>
+      <c r="X12" s="10" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr"/>
+      <c r="Z12" s="10" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr"/>
+      <c r="AB12" s="10" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr"/>
+      <c r="AD12" s="8" t="inlineStr"/>
+      <c r="AE12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1311,6 +1584,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S13" s="8" t="inlineStr"/>
+      <c r="T13" s="10" t="inlineStr"/>
+      <c r="U13" s="8" t="inlineStr"/>
+      <c r="V13" s="10" t="inlineStr"/>
+      <c r="W13" s="10" t="inlineStr"/>
+      <c r="X13" s="10" t="inlineStr"/>
+      <c r="Y13" s="10" t="inlineStr"/>
+      <c r="Z13" s="10" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr"/>
+      <c r="AB13" s="10" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr"/>
+      <c r="AD13" s="8" t="inlineStr"/>
+      <c r="AE13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1365,6 +1651,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S14" s="8" t="inlineStr"/>
+      <c r="T14" s="10" t="inlineStr"/>
+      <c r="U14" s="8" t="inlineStr"/>
+      <c r="V14" s="10" t="inlineStr"/>
+      <c r="W14" s="10" t="inlineStr"/>
+      <c r="X14" s="10" t="inlineStr"/>
+      <c r="Y14" s="10" t="inlineStr"/>
+      <c r="Z14" s="10" t="inlineStr"/>
+      <c r="AA14" s="10" t="inlineStr"/>
+      <c r="AB14" s="10" t="inlineStr"/>
+      <c r="AC14" s="10" t="inlineStr"/>
+      <c r="AD14" s="8" t="inlineStr"/>
+      <c r="AE14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1419,6 +1718,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S15" s="8" t="inlineStr"/>
+      <c r="T15" s="10" t="inlineStr"/>
+      <c r="U15" s="8" t="inlineStr"/>
+      <c r="V15" s="10" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr"/>
+      <c r="X15" s="10" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr"/>
+      <c r="Z15" s="10" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr"/>
+      <c r="AB15" s="10" t="inlineStr"/>
+      <c r="AC15" s="10" t="inlineStr"/>
+      <c r="AD15" s="8" t="inlineStr"/>
+      <c r="AE15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1473,6 +1785,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S16" s="8" t="inlineStr"/>
+      <c r="T16" s="10" t="inlineStr"/>
+      <c r="U16" s="8" t="inlineStr"/>
+      <c r="V16" s="10" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr"/>
+      <c r="X16" s="10" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr"/>
+      <c r="Z16" s="10" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr"/>
+      <c r="AB16" s="10" t="inlineStr"/>
+      <c r="AC16" s="10" t="inlineStr"/>
+      <c r="AD16" s="8" t="inlineStr"/>
+      <c r="AE16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1527,6 +1852,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S17" s="8" t="inlineStr"/>
+      <c r="T17" s="10" t="inlineStr"/>
+      <c r="U17" s="8" t="inlineStr"/>
+      <c r="V17" s="10" t="inlineStr"/>
+      <c r="W17" s="10" t="inlineStr"/>
+      <c r="X17" s="10" t="inlineStr"/>
+      <c r="Y17" s="10" t="inlineStr"/>
+      <c r="Z17" s="10" t="inlineStr"/>
+      <c r="AA17" s="10" t="inlineStr"/>
+      <c r="AB17" s="10" t="inlineStr"/>
+      <c r="AC17" s="10" t="inlineStr"/>
+      <c r="AD17" s="8" t="inlineStr"/>
+      <c r="AE17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1581,6 +1919,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S18" s="8" t="inlineStr"/>
+      <c r="T18" s="10" t="inlineStr"/>
+      <c r="U18" s="8" t="inlineStr"/>
+      <c r="V18" s="10" t="inlineStr"/>
+      <c r="W18" s="10" t="inlineStr"/>
+      <c r="X18" s="10" t="inlineStr"/>
+      <c r="Y18" s="10" t="inlineStr"/>
+      <c r="Z18" s="10" t="inlineStr"/>
+      <c r="AA18" s="10" t="inlineStr"/>
+      <c r="AB18" s="10" t="inlineStr"/>
+      <c r="AC18" s="10" t="inlineStr"/>
+      <c r="AD18" s="8" t="inlineStr"/>
+      <c r="AE18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1635,6 +1986,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S19" s="8" t="inlineStr"/>
+      <c r="T19" s="10" t="inlineStr"/>
+      <c r="U19" s="8" t="inlineStr"/>
+      <c r="V19" s="10" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr"/>
+      <c r="X19" s="10" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr"/>
+      <c r="Z19" s="10" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr"/>
+      <c r="AB19" s="10" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr"/>
+      <c r="AD19" s="8" t="inlineStr"/>
+      <c r="AE19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1689,6 +2053,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S20" s="8" t="inlineStr"/>
+      <c r="T20" s="10" t="inlineStr"/>
+      <c r="U20" s="8" t="inlineStr"/>
+      <c r="V20" s="10" t="inlineStr"/>
+      <c r="W20" s="10" t="inlineStr"/>
+      <c r="X20" s="10" t="inlineStr"/>
+      <c r="Y20" s="10" t="inlineStr"/>
+      <c r="Z20" s="10" t="inlineStr"/>
+      <c r="AA20" s="10" t="inlineStr"/>
+      <c r="AB20" s="10" t="inlineStr"/>
+      <c r="AC20" s="10" t="inlineStr"/>
+      <c r="AD20" s="8" t="inlineStr"/>
+      <c r="AE20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1743,6 +2120,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S21" s="8" t="inlineStr"/>
+      <c r="T21" s="10" t="inlineStr"/>
+      <c r="U21" s="8" t="inlineStr"/>
+      <c r="V21" s="10" t="inlineStr"/>
+      <c r="W21" s="10" t="inlineStr"/>
+      <c r="X21" s="10" t="inlineStr"/>
+      <c r="Y21" s="10" t="inlineStr"/>
+      <c r="Z21" s="10" t="inlineStr"/>
+      <c r="AA21" s="10" t="inlineStr"/>
+      <c r="AB21" s="10" t="inlineStr"/>
+      <c r="AC21" s="10" t="inlineStr"/>
+      <c r="AD21" s="8" t="inlineStr"/>
+      <c r="AE21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1797,6 +2187,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr"/>
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="5" t="inlineStr"/>
+      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="Z22" s="5" t="inlineStr"/>
+      <c r="AA22" s="5" t="inlineStr"/>
+      <c r="AB22" s="5" t="inlineStr"/>
+      <c r="AC22" s="5" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1851,6 +2254,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr"/>
+      <c r="W23" s="5" t="inlineStr"/>
+      <c r="X23" s="5" t="inlineStr"/>
+      <c r="Y23" s="5" t="inlineStr"/>
+      <c r="Z23" s="5" t="inlineStr"/>
+      <c r="AA23" s="5" t="inlineStr"/>
+      <c r="AB23" s="5" t="inlineStr"/>
+      <c r="AC23" s="5" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1905,6 +2321,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr"/>
+      <c r="W24" s="5" t="inlineStr"/>
+      <c r="X24" s="5" t="inlineStr"/>
+      <c r="Y24" s="5" t="inlineStr"/>
+      <c r="Z24" s="5" t="inlineStr"/>
+      <c r="AA24" s="5" t="inlineStr"/>
+      <c r="AB24" s="5" t="inlineStr"/>
+      <c r="AC24" s="5" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1959,6 +2388,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr"/>
+      <c r="W25" s="5" t="inlineStr"/>
+      <c r="X25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="Z25" s="5" t="inlineStr"/>
+      <c r="AA25" s="5" t="inlineStr"/>
+      <c r="AB25" s="5" t="inlineStr"/>
+      <c r="AC25" s="5" t="inlineStr"/>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2013,6 +2455,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr"/>
+      <c r="W26" s="5" t="inlineStr"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="Z26" s="5" t="inlineStr"/>
+      <c r="AA26" s="5" t="inlineStr"/>
+      <c r="AB26" s="5" t="inlineStr"/>
+      <c r="AC26" s="5" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2067,6 +2522,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="Z27" s="5" t="inlineStr"/>
+      <c r="AA27" s="5" t="inlineStr"/>
+      <c r="AB27" s="5" t="inlineStr"/>
+      <c r="AC27" s="5" t="inlineStr"/>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2141,6 +2609,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr"/>
+      <c r="W28" s="5" t="inlineStr"/>
+      <c r="X28" s="5" t="inlineStr"/>
+      <c r="Y28" s="5" t="inlineStr"/>
+      <c r="Z28" s="5" t="inlineStr"/>
+      <c r="AA28" s="5" t="inlineStr"/>
+      <c r="AB28" s="5" t="inlineStr"/>
+      <c r="AC28" s="5" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2195,6 +2676,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr"/>
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
+      <c r="Z29" s="5" t="inlineStr"/>
+      <c r="AA29" s="5" t="inlineStr"/>
+      <c r="AB29" s="5" t="inlineStr"/>
+      <c r="AC29" s="5" t="inlineStr"/>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2249,6 +2743,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr"/>
+      <c r="W30" s="5" t="inlineStr"/>
+      <c r="X30" s="5" t="inlineStr"/>
+      <c r="Y30" s="5" t="inlineStr"/>
+      <c r="Z30" s="5" t="inlineStr"/>
+      <c r="AA30" s="5" t="inlineStr"/>
+      <c r="AB30" s="5" t="inlineStr"/>
+      <c r="AC30" s="5" t="inlineStr"/>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2323,6 +2830,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr"/>
+      <c r="W31" s="5" t="inlineStr"/>
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr"/>
+      <c r="Z31" s="5" t="inlineStr"/>
+      <c r="AA31" s="5" t="inlineStr"/>
+      <c r="AB31" s="5" t="inlineStr"/>
+      <c r="AC31" s="5" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2397,6 +2917,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr"/>
+      <c r="W32" s="5" t="inlineStr"/>
+      <c r="X32" s="5" t="inlineStr"/>
+      <c r="Y32" s="5" t="inlineStr"/>
+      <c r="Z32" s="5" t="inlineStr"/>
+      <c r="AA32" s="5" t="inlineStr"/>
+      <c r="AB32" s="5" t="inlineStr"/>
+      <c r="AC32" s="5" t="inlineStr"/>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2471,6 +3004,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="5" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr"/>
+      <c r="W33" s="5" t="inlineStr"/>
+      <c r="X33" s="5" t="inlineStr"/>
+      <c r="Y33" s="5" t="inlineStr"/>
+      <c r="Z33" s="5" t="inlineStr"/>
+      <c r="AA33" s="5" t="inlineStr"/>
+      <c r="AB33" s="5" t="inlineStr"/>
+      <c r="AC33" s="5" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2545,6 +3091,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr"/>
+      <c r="W34" s="5" t="inlineStr"/>
+      <c r="X34" s="5" t="inlineStr"/>
+      <c r="Y34" s="5" t="inlineStr"/>
+      <c r="Z34" s="5" t="inlineStr"/>
+      <c r="AA34" s="5" t="inlineStr"/>
+      <c r="AB34" s="5" t="inlineStr"/>
+      <c r="AC34" s="5" t="inlineStr"/>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2619,6 +3178,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr"/>
+      <c r="W35" s="5" t="inlineStr"/>
+      <c r="X35" s="5" t="inlineStr"/>
+      <c r="Y35" s="5" t="inlineStr"/>
+      <c r="Z35" s="5" t="inlineStr"/>
+      <c r="AA35" s="5" t="inlineStr"/>
+      <c r="AB35" s="5" t="inlineStr"/>
+      <c r="AC35" s="5" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2673,6 +3245,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="5" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr"/>
+      <c r="W36" s="5" t="inlineStr"/>
+      <c r="X36" s="5" t="inlineStr"/>
+      <c r="Y36" s="5" t="inlineStr"/>
+      <c r="Z36" s="5" t="inlineStr"/>
+      <c r="AA36" s="5" t="inlineStr"/>
+      <c r="AB36" s="5" t="inlineStr"/>
+      <c r="AC36" s="5" t="inlineStr"/>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2747,6 +3332,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr"/>
+      <c r="W37" s="5" t="inlineStr"/>
+      <c r="X37" s="5" t="inlineStr"/>
+      <c r="Y37" s="5" t="inlineStr"/>
+      <c r="Z37" s="5" t="inlineStr"/>
+      <c r="AA37" s="5" t="inlineStr"/>
+      <c r="AB37" s="5" t="inlineStr"/>
+      <c r="AC37" s="5" t="inlineStr"/>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2821,6 +3419,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="5" t="inlineStr"/>
+      <c r="X38" s="5" t="inlineStr"/>
+      <c r="Y38" s="5" t="inlineStr"/>
+      <c r="Z38" s="5" t="inlineStr"/>
+      <c r="AA38" s="5" t="inlineStr"/>
+      <c r="AB38" s="5" t="inlineStr"/>
+      <c r="AC38" s="5" t="inlineStr"/>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2875,6 +3486,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr"/>
+      <c r="W39" s="5" t="inlineStr"/>
+      <c r="X39" s="5" t="inlineStr"/>
+      <c r="Y39" s="5" t="inlineStr"/>
+      <c r="Z39" s="5" t="inlineStr"/>
+      <c r="AA39" s="5" t="inlineStr"/>
+      <c r="AB39" s="5" t="inlineStr"/>
+      <c r="AC39" s="5" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2929,6 +3553,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr"/>
+      <c r="W40" s="5" t="inlineStr"/>
+      <c r="X40" s="5" t="inlineStr"/>
+      <c r="Y40" s="5" t="inlineStr"/>
+      <c r="Z40" s="5" t="inlineStr"/>
+      <c r="AA40" s="5" t="inlineStr"/>
+      <c r="AB40" s="5" t="inlineStr"/>
+      <c r="AC40" s="5" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3003,6 +3640,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr"/>
+      <c r="W41" s="5" t="inlineStr"/>
+      <c r="X41" s="5" t="inlineStr"/>
+      <c r="Y41" s="5" t="inlineStr"/>
+      <c r="Z41" s="5" t="inlineStr"/>
+      <c r="AA41" s="5" t="inlineStr"/>
+      <c r="AB41" s="5" t="inlineStr"/>
+      <c r="AC41" s="5" t="inlineStr"/>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3057,6 +3707,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr"/>
+      <c r="W42" s="5" t="inlineStr"/>
+      <c r="X42" s="5" t="inlineStr"/>
+      <c r="Y42" s="5" t="inlineStr"/>
+      <c r="Z42" s="5" t="inlineStr"/>
+      <c r="AA42" s="5" t="inlineStr"/>
+      <c r="AB42" s="5" t="inlineStr"/>
+      <c r="AC42" s="5" t="inlineStr"/>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -3111,6 +3774,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr"/>
+      <c r="W43" s="5" t="inlineStr"/>
+      <c r="X43" s="5" t="inlineStr"/>
+      <c r="Y43" s="5" t="inlineStr"/>
+      <c r="Z43" s="5" t="inlineStr"/>
+      <c r="AA43" s="5" t="inlineStr"/>
+      <c r="AB43" s="5" t="inlineStr"/>
+      <c r="AC43" s="5" t="inlineStr"/>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3185,6 +3861,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="5" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr"/>
+      <c r="W44" s="5" t="inlineStr"/>
+      <c r="X44" s="5" t="inlineStr"/>
+      <c r="Y44" s="5" t="inlineStr"/>
+      <c r="Z44" s="5" t="inlineStr"/>
+      <c r="AA44" s="5" t="inlineStr"/>
+      <c r="AB44" s="5" t="inlineStr"/>
+      <c r="AC44" s="5" t="inlineStr"/>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -3259,6 +3948,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr"/>
+      <c r="W45" s="5" t="inlineStr"/>
+      <c r="X45" s="5" t="inlineStr"/>
+      <c r="Y45" s="5" t="inlineStr"/>
+      <c r="Z45" s="5" t="inlineStr"/>
+      <c r="AA45" s="5" t="inlineStr"/>
+      <c r="AB45" s="5" t="inlineStr"/>
+      <c r="AC45" s="5" t="inlineStr"/>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -3333,6 +4035,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr"/>
+      <c r="W46" s="5" t="inlineStr"/>
+      <c r="X46" s="5" t="inlineStr"/>
+      <c r="Y46" s="5" t="inlineStr"/>
+      <c r="Z46" s="5" t="inlineStr"/>
+      <c r="AA46" s="5" t="inlineStr"/>
+      <c r="AB46" s="5" t="inlineStr"/>
+      <c r="AC46" s="5" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3387,6 +4102,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr"/>
+      <c r="W47" s="5" t="inlineStr"/>
+      <c r="X47" s="5" t="inlineStr"/>
+      <c r="Y47" s="5" t="inlineStr"/>
+      <c r="Z47" s="5" t="inlineStr"/>
+      <c r="AA47" s="5" t="inlineStr"/>
+      <c r="AB47" s="5" t="inlineStr"/>
+      <c r="AC47" s="5" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -3441,6 +4169,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr"/>
+      <c r="W48" s="5" t="inlineStr"/>
+      <c r="X48" s="5" t="inlineStr"/>
+      <c r="Y48" s="5" t="inlineStr"/>
+      <c r="Z48" s="5" t="inlineStr"/>
+      <c r="AA48" s="5" t="inlineStr"/>
+      <c r="AB48" s="5" t="inlineStr"/>
+      <c r="AC48" s="5" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -3515,6 +4256,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr"/>
+      <c r="W49" s="5" t="inlineStr"/>
+      <c r="X49" s="5" t="inlineStr"/>
+      <c r="Y49" s="5" t="inlineStr"/>
+      <c r="Z49" s="5" t="inlineStr"/>
+      <c r="AA49" s="5" t="inlineStr"/>
+      <c r="AB49" s="5" t="inlineStr"/>
+      <c r="AC49" s="5" t="inlineStr"/>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -3589,6 +4343,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="5" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr"/>
+      <c r="W50" s="5" t="inlineStr"/>
+      <c r="X50" s="5" t="inlineStr"/>
+      <c r="Y50" s="5" t="inlineStr"/>
+      <c r="Z50" s="5" t="inlineStr"/>
+      <c r="AA50" s="5" t="inlineStr"/>
+      <c r="AB50" s="5" t="inlineStr"/>
+      <c r="AC50" s="5" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -3643,6 +4410,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="5" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr"/>
+      <c r="W51" s="5" t="inlineStr"/>
+      <c r="X51" s="5" t="inlineStr"/>
+      <c r="Y51" s="5" t="inlineStr"/>
+      <c r="Z51" s="5" t="inlineStr"/>
+      <c r="AA51" s="5" t="inlineStr"/>
+      <c r="AB51" s="5" t="inlineStr"/>
+      <c r="AC51" s="5" t="inlineStr"/>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -3697,6 +4477,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr"/>
+      <c r="W52" s="5" t="inlineStr"/>
+      <c r="X52" s="5" t="inlineStr"/>
+      <c r="Y52" s="5" t="inlineStr"/>
+      <c r="Z52" s="5" t="inlineStr"/>
+      <c r="AA52" s="5" t="inlineStr"/>
+      <c r="AB52" s="5" t="inlineStr"/>
+      <c r="AC52" s="5" t="inlineStr"/>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -3751,6 +4544,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr"/>
+      <c r="W53" s="5" t="inlineStr"/>
+      <c r="X53" s="5" t="inlineStr"/>
+      <c r="Y53" s="5" t="inlineStr"/>
+      <c r="Z53" s="5" t="inlineStr"/>
+      <c r="AA53" s="5" t="inlineStr"/>
+      <c r="AB53" s="5" t="inlineStr"/>
+      <c r="AC53" s="5" t="inlineStr"/>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3825,6 +4631,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr"/>
+      <c r="W54" s="5" t="inlineStr"/>
+      <c r="X54" s="5" t="inlineStr"/>
+      <c r="Y54" s="5" t="inlineStr"/>
+      <c r="Z54" s="5" t="inlineStr"/>
+      <c r="AA54" s="5" t="inlineStr"/>
+      <c r="AB54" s="5" t="inlineStr"/>
+      <c r="AC54" s="5" t="inlineStr"/>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3879,6 +4698,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr"/>
+      <c r="W55" s="5" t="inlineStr"/>
+      <c r="X55" s="5" t="inlineStr"/>
+      <c r="Y55" s="5" t="inlineStr"/>
+      <c r="Z55" s="5" t="inlineStr"/>
+      <c r="AA55" s="5" t="inlineStr"/>
+      <c r="AB55" s="5" t="inlineStr"/>
+      <c r="AC55" s="5" t="inlineStr"/>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3933,6 +4765,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="5" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
+      <c r="X56" s="5" t="inlineStr"/>
+      <c r="Y56" s="5" t="inlineStr"/>
+      <c r="Z56" s="5" t="inlineStr"/>
+      <c r="AA56" s="5" t="inlineStr"/>
+      <c r="AB56" s="5" t="inlineStr"/>
+      <c r="AC56" s="5" t="inlineStr"/>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -4007,6 +4852,19 @@
           <t>理杏仁公开页面</t>
         </is>
       </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr"/>
+      <c r="W57" s="5" t="inlineStr"/>
+      <c r="X57" s="5" t="inlineStr"/>
+      <c r="Y57" s="5" t="inlineStr"/>
+      <c r="Z57" s="5" t="inlineStr"/>
+      <c r="AA57" s="5" t="inlineStr"/>
+      <c r="AB57" s="5" t="inlineStr"/>
+      <c r="AC57" s="5" t="inlineStr"/>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -4061,6 +4919,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="5" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr"/>
+      <c r="W58" s="5" t="inlineStr"/>
+      <c r="X58" s="5" t="inlineStr"/>
+      <c r="Y58" s="5" t="inlineStr"/>
+      <c r="Z58" s="5" t="inlineStr"/>
+      <c r="AA58" s="5" t="inlineStr"/>
+      <c r="AB58" s="5" t="inlineStr"/>
+      <c r="AC58" s="5" t="inlineStr"/>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -4115,6 +4986,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="5" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr"/>
+      <c r="W59" s="5" t="inlineStr"/>
+      <c r="X59" s="5" t="inlineStr"/>
+      <c r="Y59" s="5" t="inlineStr"/>
+      <c r="Z59" s="5" t="inlineStr"/>
+      <c r="AA59" s="5" t="inlineStr"/>
+      <c r="AB59" s="5" t="inlineStr"/>
+      <c r="AC59" s="5" t="inlineStr"/>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -4173,6 +5057,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="5" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr"/>
+      <c r="V60" s="5" t="inlineStr"/>
+      <c r="W60" s="5" t="inlineStr"/>
+      <c r="X60" s="5" t="inlineStr"/>
+      <c r="Y60" s="5" t="inlineStr"/>
+      <c r="Z60" s="5" t="inlineStr"/>
+      <c r="AA60" s="5" t="inlineStr"/>
+      <c r="AB60" s="5" t="inlineStr"/>
+      <c r="AC60" s="5" t="inlineStr"/>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -4231,6 +5128,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="5" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr"/>
+      <c r="W61" s="5" t="inlineStr"/>
+      <c r="X61" s="5" t="inlineStr"/>
+      <c r="Y61" s="5" t="inlineStr"/>
+      <c r="Z61" s="5" t="inlineStr"/>
+      <c r="AA61" s="5" t="inlineStr"/>
+      <c r="AB61" s="5" t="inlineStr"/>
+      <c r="AC61" s="5" t="inlineStr"/>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -4289,6 +5199,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="5" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr"/>
+      <c r="W62" s="5" t="inlineStr"/>
+      <c r="X62" s="5" t="inlineStr"/>
+      <c r="Y62" s="5" t="inlineStr"/>
+      <c r="Z62" s="5" t="inlineStr"/>
+      <c r="AA62" s="5" t="inlineStr"/>
+      <c r="AB62" s="5" t="inlineStr"/>
+      <c r="AC62" s="5" t="inlineStr"/>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -4347,6 +5270,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="5" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="5" t="inlineStr"/>
+      <c r="X63" s="5" t="inlineStr"/>
+      <c r="Y63" s="5" t="inlineStr"/>
+      <c r="Z63" s="5" t="inlineStr"/>
+      <c r="AA63" s="5" t="inlineStr"/>
+      <c r="AB63" s="5" t="inlineStr"/>
+      <c r="AC63" s="5" t="inlineStr"/>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4405,6 +5341,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="5" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr"/>
+      <c r="V64" s="5" t="inlineStr"/>
+      <c r="W64" s="5" t="inlineStr"/>
+      <c r="X64" s="5" t="inlineStr"/>
+      <c r="Y64" s="5" t="inlineStr"/>
+      <c r="Z64" s="5" t="inlineStr"/>
+      <c r="AA64" s="5" t="inlineStr"/>
+      <c r="AB64" s="5" t="inlineStr"/>
+      <c r="AC64" s="5" t="inlineStr"/>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -4463,6 +5412,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="5" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr"/>
+      <c r="V65" s="5" t="inlineStr"/>
+      <c r="W65" s="5" t="inlineStr"/>
+      <c r="X65" s="5" t="inlineStr"/>
+      <c r="Y65" s="5" t="inlineStr"/>
+      <c r="Z65" s="5" t="inlineStr"/>
+      <c r="AA65" s="5" t="inlineStr"/>
+      <c r="AB65" s="5" t="inlineStr"/>
+      <c r="AC65" s="5" t="inlineStr"/>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -4521,6 +5483,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="5" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr"/>
+      <c r="W66" s="5" t="inlineStr"/>
+      <c r="X66" s="5" t="inlineStr"/>
+      <c r="Y66" s="5" t="inlineStr"/>
+      <c r="Z66" s="5" t="inlineStr"/>
+      <c r="AA66" s="5" t="inlineStr"/>
+      <c r="AB66" s="5" t="inlineStr"/>
+      <c r="AC66" s="5" t="inlineStr"/>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -4579,6 +5554,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="5" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr"/>
+      <c r="W67" s="5" t="inlineStr"/>
+      <c r="X67" s="5" t="inlineStr"/>
+      <c r="Y67" s="5" t="inlineStr"/>
+      <c r="Z67" s="5" t="inlineStr"/>
+      <c r="AA67" s="5" t="inlineStr"/>
+      <c r="AB67" s="5" t="inlineStr"/>
+      <c r="AC67" s="5" t="inlineStr"/>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -4637,6 +5625,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="5" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr"/>
+      <c r="V68" s="5" t="inlineStr"/>
+      <c r="W68" s="5" t="inlineStr"/>
+      <c r="X68" s="5" t="inlineStr"/>
+      <c r="Y68" s="5" t="inlineStr"/>
+      <c r="Z68" s="5" t="inlineStr"/>
+      <c r="AA68" s="5" t="inlineStr"/>
+      <c r="AB68" s="5" t="inlineStr"/>
+      <c r="AC68" s="5" t="inlineStr"/>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -4695,6 +5696,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="5" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr"/>
+      <c r="V69" s="5" t="inlineStr"/>
+      <c r="W69" s="5" t="inlineStr"/>
+      <c r="X69" s="5" t="inlineStr"/>
+      <c r="Y69" s="5" t="inlineStr"/>
+      <c r="Z69" s="5" t="inlineStr"/>
+      <c r="AA69" s="5" t="inlineStr"/>
+      <c r="AB69" s="5" t="inlineStr"/>
+      <c r="AC69" s="5" t="inlineStr"/>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -4753,6 +5767,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="5" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr"/>
+      <c r="V70" s="5" t="inlineStr"/>
+      <c r="W70" s="5" t="inlineStr"/>
+      <c r="X70" s="5" t="inlineStr"/>
+      <c r="Y70" s="5" t="inlineStr"/>
+      <c r="Z70" s="5" t="inlineStr"/>
+      <c r="AA70" s="5" t="inlineStr"/>
+      <c r="AB70" s="5" t="inlineStr"/>
+      <c r="AC70" s="5" t="inlineStr"/>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -4811,6 +5838,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="5" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr"/>
+      <c r="V71" s="5" t="inlineStr"/>
+      <c r="W71" s="5" t="inlineStr"/>
+      <c r="X71" s="5" t="inlineStr"/>
+      <c r="Y71" s="5" t="inlineStr"/>
+      <c r="Z71" s="5" t="inlineStr"/>
+      <c r="AA71" s="5" t="inlineStr"/>
+      <c r="AB71" s="5" t="inlineStr"/>
+      <c r="AC71" s="5" t="inlineStr"/>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -4869,6 +5909,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="5" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr"/>
+      <c r="V72" s="5" t="inlineStr"/>
+      <c r="W72" s="5" t="inlineStr"/>
+      <c r="X72" s="5" t="inlineStr"/>
+      <c r="Y72" s="5" t="inlineStr"/>
+      <c r="Z72" s="5" t="inlineStr"/>
+      <c r="AA72" s="5" t="inlineStr"/>
+      <c r="AB72" s="5" t="inlineStr"/>
+      <c r="AC72" s="5" t="inlineStr"/>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -4927,6 +5980,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="5" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr"/>
+      <c r="V73" s="5" t="inlineStr"/>
+      <c r="W73" s="5" t="inlineStr"/>
+      <c r="X73" s="5" t="inlineStr"/>
+      <c r="Y73" s="5" t="inlineStr"/>
+      <c r="Z73" s="5" t="inlineStr"/>
+      <c r="AA73" s="5" t="inlineStr"/>
+      <c r="AB73" s="5" t="inlineStr"/>
+      <c r="AC73" s="5" t="inlineStr"/>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -4985,6 +6051,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="5" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr"/>
+      <c r="V74" s="5" t="inlineStr"/>
+      <c r="W74" s="5" t="inlineStr"/>
+      <c r="X74" s="5" t="inlineStr"/>
+      <c r="Y74" s="5" t="inlineStr"/>
+      <c r="Z74" s="5" t="inlineStr"/>
+      <c r="AA74" s="5" t="inlineStr"/>
+      <c r="AB74" s="5" t="inlineStr"/>
+      <c r="AC74" s="5" t="inlineStr"/>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -5043,6 +6122,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="5" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr"/>
+      <c r="V75" s="5" t="inlineStr"/>
+      <c r="W75" s="5" t="inlineStr"/>
+      <c r="X75" s="5" t="inlineStr"/>
+      <c r="Y75" s="5" t="inlineStr"/>
+      <c r="Z75" s="5" t="inlineStr"/>
+      <c r="AA75" s="5" t="inlineStr"/>
+      <c r="AB75" s="5" t="inlineStr"/>
+      <c r="AC75" s="5" t="inlineStr"/>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -5101,6 +6193,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="5" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr"/>
+      <c r="V76" s="5" t="inlineStr"/>
+      <c r="W76" s="5" t="inlineStr"/>
+      <c r="X76" s="5" t="inlineStr"/>
+      <c r="Y76" s="5" t="inlineStr"/>
+      <c r="Z76" s="5" t="inlineStr"/>
+      <c r="AA76" s="5" t="inlineStr"/>
+      <c r="AB76" s="5" t="inlineStr"/>
+      <c r="AC76" s="5" t="inlineStr"/>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -5159,6 +6264,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S77" s="3" t="inlineStr"/>
+      <c r="T77" s="5" t="inlineStr"/>
+      <c r="U77" s="3" t="inlineStr"/>
+      <c r="V77" s="5" t="inlineStr"/>
+      <c r="W77" s="5" t="inlineStr"/>
+      <c r="X77" s="5" t="inlineStr"/>
+      <c r="Y77" s="5" t="inlineStr"/>
+      <c r="Z77" s="5" t="inlineStr"/>
+      <c r="AA77" s="5" t="inlineStr"/>
+      <c r="AB77" s="5" t="inlineStr"/>
+      <c r="AC77" s="5" t="inlineStr"/>
+      <c r="AD77" s="3" t="inlineStr"/>
+      <c r="AE77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -5217,6 +6335,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S78" s="3" t="inlineStr"/>
+      <c r="T78" s="5" t="inlineStr"/>
+      <c r="U78" s="3" t="inlineStr"/>
+      <c r="V78" s="5" t="inlineStr"/>
+      <c r="W78" s="5" t="inlineStr"/>
+      <c r="X78" s="5" t="inlineStr"/>
+      <c r="Y78" s="5" t="inlineStr"/>
+      <c r="Z78" s="5" t="inlineStr"/>
+      <c r="AA78" s="5" t="inlineStr"/>
+      <c r="AB78" s="5" t="inlineStr"/>
+      <c r="AC78" s="5" t="inlineStr"/>
+      <c r="AD78" s="3" t="inlineStr"/>
+      <c r="AE78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -5275,6 +6406,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S79" s="3" t="inlineStr"/>
+      <c r="T79" s="5" t="inlineStr"/>
+      <c r="U79" s="3" t="inlineStr"/>
+      <c r="V79" s="5" t="inlineStr"/>
+      <c r="W79" s="5" t="inlineStr"/>
+      <c r="X79" s="5" t="inlineStr"/>
+      <c r="Y79" s="5" t="inlineStr"/>
+      <c r="Z79" s="5" t="inlineStr"/>
+      <c r="AA79" s="5" t="inlineStr"/>
+      <c r="AB79" s="5" t="inlineStr"/>
+      <c r="AC79" s="5" t="inlineStr"/>
+      <c r="AD79" s="3" t="inlineStr"/>
+      <c r="AE79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -5333,6 +6477,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S80" s="3" t="inlineStr"/>
+      <c r="T80" s="5" t="inlineStr"/>
+      <c r="U80" s="3" t="inlineStr"/>
+      <c r="V80" s="5" t="inlineStr"/>
+      <c r="W80" s="5" t="inlineStr"/>
+      <c r="X80" s="5" t="inlineStr"/>
+      <c r="Y80" s="5" t="inlineStr"/>
+      <c r="Z80" s="5" t="inlineStr"/>
+      <c r="AA80" s="5" t="inlineStr"/>
+      <c r="AB80" s="5" t="inlineStr"/>
+      <c r="AC80" s="5" t="inlineStr"/>
+      <c r="AD80" s="3" t="inlineStr"/>
+      <c r="AE80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -5391,6 +6548,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S81" s="3" t="inlineStr"/>
+      <c r="T81" s="5" t="inlineStr"/>
+      <c r="U81" s="3" t="inlineStr"/>
+      <c r="V81" s="5" t="inlineStr"/>
+      <c r="W81" s="5" t="inlineStr"/>
+      <c r="X81" s="5" t="inlineStr"/>
+      <c r="Y81" s="5" t="inlineStr"/>
+      <c r="Z81" s="5" t="inlineStr"/>
+      <c r="AA81" s="5" t="inlineStr"/>
+      <c r="AB81" s="5" t="inlineStr"/>
+      <c r="AC81" s="5" t="inlineStr"/>
+      <c r="AD81" s="3" t="inlineStr"/>
+      <c r="AE81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -5449,6 +6619,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S82" s="3" t="inlineStr"/>
+      <c r="T82" s="5" t="inlineStr"/>
+      <c r="U82" s="3" t="inlineStr"/>
+      <c r="V82" s="5" t="inlineStr"/>
+      <c r="W82" s="5" t="inlineStr"/>
+      <c r="X82" s="5" t="inlineStr"/>
+      <c r="Y82" s="5" t="inlineStr"/>
+      <c r="Z82" s="5" t="inlineStr"/>
+      <c r="AA82" s="5" t="inlineStr"/>
+      <c r="AB82" s="5" t="inlineStr"/>
+      <c r="AC82" s="5" t="inlineStr"/>
+      <c r="AD82" s="3" t="inlineStr"/>
+      <c r="AE82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -5507,6 +6690,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S83" s="3" t="inlineStr"/>
+      <c r="T83" s="5" t="inlineStr"/>
+      <c r="U83" s="3" t="inlineStr"/>
+      <c r="V83" s="5" t="inlineStr"/>
+      <c r="W83" s="5" t="inlineStr"/>
+      <c r="X83" s="5" t="inlineStr"/>
+      <c r="Y83" s="5" t="inlineStr"/>
+      <c r="Z83" s="5" t="inlineStr"/>
+      <c r="AA83" s="5" t="inlineStr"/>
+      <c r="AB83" s="5" t="inlineStr"/>
+      <c r="AC83" s="5" t="inlineStr"/>
+      <c r="AD83" s="3" t="inlineStr"/>
+      <c r="AE83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -5565,6 +6761,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S84" s="3" t="inlineStr"/>
+      <c r="T84" s="5" t="inlineStr"/>
+      <c r="U84" s="3" t="inlineStr"/>
+      <c r="V84" s="5" t="inlineStr"/>
+      <c r="W84" s="5" t="inlineStr"/>
+      <c r="X84" s="5" t="inlineStr"/>
+      <c r="Y84" s="5" t="inlineStr"/>
+      <c r="Z84" s="5" t="inlineStr"/>
+      <c r="AA84" s="5" t="inlineStr"/>
+      <c r="AB84" s="5" t="inlineStr"/>
+      <c r="AC84" s="5" t="inlineStr"/>
+      <c r="AD84" s="3" t="inlineStr"/>
+      <c r="AE84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -5623,6 +6832,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S85" s="3" t="inlineStr"/>
+      <c r="T85" s="5" t="inlineStr"/>
+      <c r="U85" s="3" t="inlineStr"/>
+      <c r="V85" s="5" t="inlineStr"/>
+      <c r="W85" s="5" t="inlineStr"/>
+      <c r="X85" s="5" t="inlineStr"/>
+      <c r="Y85" s="5" t="inlineStr"/>
+      <c r="Z85" s="5" t="inlineStr"/>
+      <c r="AA85" s="5" t="inlineStr"/>
+      <c r="AB85" s="5" t="inlineStr"/>
+      <c r="AC85" s="5" t="inlineStr"/>
+      <c r="AD85" s="3" t="inlineStr"/>
+      <c r="AE85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -5681,6 +6903,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S86" s="3" t="inlineStr"/>
+      <c r="T86" s="5" t="inlineStr"/>
+      <c r="U86" s="3" t="inlineStr"/>
+      <c r="V86" s="5" t="inlineStr"/>
+      <c r="W86" s="5" t="inlineStr"/>
+      <c r="X86" s="5" t="inlineStr"/>
+      <c r="Y86" s="5" t="inlineStr"/>
+      <c r="Z86" s="5" t="inlineStr"/>
+      <c r="AA86" s="5" t="inlineStr"/>
+      <c r="AB86" s="5" t="inlineStr"/>
+      <c r="AC86" s="5" t="inlineStr"/>
+      <c r="AD86" s="3" t="inlineStr"/>
+      <c r="AE86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -5739,6 +6974,19 @@
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S87" s="3" t="inlineStr"/>
+      <c r="T87" s="5" t="inlineStr"/>
+      <c r="U87" s="3" t="inlineStr"/>
+      <c r="V87" s="5" t="inlineStr"/>
+      <c r="W87" s="5" t="inlineStr"/>
+      <c r="X87" s="5" t="inlineStr"/>
+      <c r="Y87" s="5" t="inlineStr"/>
+      <c r="Z87" s="5" t="inlineStr"/>
+      <c r="AA87" s="5" t="inlineStr"/>
+      <c r="AB87" s="5" t="inlineStr"/>
+      <c r="AC87" s="5" t="inlineStr"/>
+      <c r="AD87" s="3" t="inlineStr"/>
+      <c r="AE87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -5760,7 +7008,7 @@
       <c r="E88" s="4" t="n">
         <v>-15.96361099166238</v>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="n"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -5788,18 +7036,1055 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="N88" s="3" t="inlineStr"/>
-      <c r="O88" s="4" t="inlineStr"/>
-      <c r="P88" s="4" t="inlineStr"/>
-      <c r="Q88" s="4" t="inlineStr"/>
+      <c r="N88" s="3" t="n"/>
+      <c r="O88" s="4" t="n"/>
+      <c r="P88" s="4" t="n"/>
+      <c r="Q88" s="4" t="n"/>
       <c r="R88" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
+      <c r="S88" s="3" t="inlineStr"/>
+      <c r="T88" s="5" t="inlineStr"/>
+      <c r="U88" s="3" t="inlineStr"/>
+      <c r="V88" s="5" t="inlineStr"/>
+      <c r="W88" s="5" t="inlineStr"/>
+      <c r="X88" s="5" t="inlineStr"/>
+      <c r="Y88" s="5" t="inlineStr"/>
+      <c r="Z88" s="5" t="inlineStr"/>
+      <c r="AA88" s="5" t="inlineStr"/>
+      <c r="AB88" s="5" t="inlineStr"/>
+      <c r="AC88" s="5" t="inlineStr"/>
+      <c r="AD88" s="3" t="inlineStr"/>
+      <c r="AE88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>1.379517548940123</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>1.6864</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>2.4636</v>
+      </c>
+      <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="n"/>
+      <c r="O89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
+      <c r="Q89" s="4" t="n"/>
+      <c r="R89" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S89" s="3" t="inlineStr"/>
+      <c r="T89" s="5" t="inlineStr"/>
+      <c r="U89" s="3" t="inlineStr"/>
+      <c r="V89" s="5" t="inlineStr"/>
+      <c r="W89" s="5" t="inlineStr"/>
+      <c r="X89" s="5" t="inlineStr"/>
+      <c r="Y89" s="5" t="inlineStr"/>
+      <c r="Z89" s="5" t="inlineStr"/>
+      <c r="AA89" s="5" t="inlineStr"/>
+      <c r="AB89" s="5" t="inlineStr"/>
+      <c r="AC89" s="5" t="inlineStr"/>
+      <c r="AD89" s="3" t="inlineStr"/>
+      <c r="AE89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="6" t="inlineStr"/>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="n"/>
+      <c r="O90" s="4" t="n"/>
+      <c r="P90" s="4" t="n"/>
+      <c r="Q90" s="4" t="n"/>
+      <c r="R90" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S90" s="3" t="inlineStr"/>
+      <c r="T90" s="5" t="inlineStr"/>
+      <c r="U90" s="3" t="inlineStr"/>
+      <c r="V90" s="5" t="inlineStr"/>
+      <c r="W90" s="5" t="inlineStr"/>
+      <c r="X90" s="5" t="inlineStr"/>
+      <c r="Y90" s="5" t="inlineStr"/>
+      <c r="Z90" s="5" t="inlineStr"/>
+      <c r="AA90" s="5" t="inlineStr"/>
+      <c r="AB90" s="5" t="inlineStr"/>
+      <c r="AC90" s="5" t="inlineStr"/>
+      <c r="AD90" s="3" t="inlineStr"/>
+      <c r="AE90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="n"/>
+      <c r="O91" s="4" t="n"/>
+      <c r="P91" s="4" t="n"/>
+      <c r="Q91" s="4" t="n"/>
+      <c r="R91" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S91" s="3" t="inlineStr"/>
+      <c r="T91" s="5" t="inlineStr"/>
+      <c r="U91" s="3" t="inlineStr"/>
+      <c r="V91" s="5" t="inlineStr"/>
+      <c r="W91" s="5" t="inlineStr"/>
+      <c r="X91" s="5" t="inlineStr"/>
+      <c r="Y91" s="5" t="inlineStr"/>
+      <c r="Z91" s="5" t="inlineStr"/>
+      <c r="AA91" s="5" t="inlineStr"/>
+      <c r="AB91" s="5" t="inlineStr"/>
+      <c r="AC91" s="5" t="inlineStr"/>
+      <c r="AD91" s="3" t="inlineStr"/>
+      <c r="AE91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="6" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="n"/>
+      <c r="O92" s="4" t="n"/>
+      <c r="P92" s="4" t="n"/>
+      <c r="Q92" s="4" t="n"/>
+      <c r="R92" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S92" s="3" t="inlineStr"/>
+      <c r="T92" s="5" t="inlineStr"/>
+      <c r="U92" s="3" t="inlineStr"/>
+      <c r="V92" s="5" t="inlineStr"/>
+      <c r="W92" s="5" t="inlineStr"/>
+      <c r="X92" s="5" t="inlineStr"/>
+      <c r="Y92" s="5" t="inlineStr"/>
+      <c r="Z92" s="5" t="inlineStr"/>
+      <c r="AA92" s="5" t="inlineStr"/>
+      <c r="AB92" s="5" t="inlineStr"/>
+      <c r="AC92" s="5" t="inlineStr"/>
+      <c r="AD92" s="3" t="inlineStr"/>
+      <c r="AE92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="n"/>
+      <c r="O93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
+      <c r="Q93" s="4" t="n"/>
+      <c r="R93" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr"/>
+      <c r="T93" s="5" t="inlineStr"/>
+      <c r="U93" s="3" t="inlineStr"/>
+      <c r="V93" s="5" t="inlineStr"/>
+      <c r="W93" s="5" t="inlineStr"/>
+      <c r="X93" s="5" t="inlineStr"/>
+      <c r="Y93" s="5" t="inlineStr"/>
+      <c r="Z93" s="5" t="inlineStr"/>
+      <c r="AA93" s="5" t="inlineStr"/>
+      <c r="AB93" s="5" t="inlineStr"/>
+      <c r="AC93" s="5" t="inlineStr"/>
+      <c r="AD93" s="3" t="inlineStr"/>
+      <c r="AE93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="n"/>
+      <c r="O94" s="4" t="n"/>
+      <c r="P94" s="4" t="n"/>
+      <c r="Q94" s="4" t="n"/>
+      <c r="R94" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="inlineStr"/>
+      <c r="T94" s="5" t="inlineStr"/>
+      <c r="U94" s="3" t="inlineStr"/>
+      <c r="V94" s="5" t="inlineStr"/>
+      <c r="W94" s="5" t="inlineStr"/>
+      <c r="X94" s="5" t="inlineStr"/>
+      <c r="Y94" s="5" t="inlineStr"/>
+      <c r="Z94" s="5" t="inlineStr"/>
+      <c r="AA94" s="5" t="inlineStr"/>
+      <c r="AB94" s="5" t="inlineStr"/>
+      <c r="AC94" s="5" t="inlineStr"/>
+      <c r="AD94" s="3" t="inlineStr"/>
+      <c r="AE94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="n"/>
+      <c r="O95" s="4" t="n"/>
+      <c r="P95" s="4" t="n"/>
+      <c r="Q95" s="4" t="n"/>
+      <c r="R95" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S95" s="3" t="inlineStr"/>
+      <c r="T95" s="5" t="inlineStr"/>
+      <c r="U95" s="3" t="inlineStr"/>
+      <c r="V95" s="5" t="inlineStr"/>
+      <c r="W95" s="5" t="inlineStr"/>
+      <c r="X95" s="5" t="inlineStr"/>
+      <c r="Y95" s="5" t="inlineStr"/>
+      <c r="Z95" s="5" t="inlineStr"/>
+      <c r="AA95" s="5" t="inlineStr"/>
+      <c r="AB95" s="5" t="inlineStr"/>
+      <c r="AC95" s="5" t="inlineStr"/>
+      <c r="AD95" s="3" t="inlineStr"/>
+      <c r="AE95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>-0.5751911270705401</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="6" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="n"/>
+      <c r="O96" s="4" t="n"/>
+      <c r="P96" s="4" t="n"/>
+      <c r="Q96" s="4" t="n"/>
+      <c r="R96" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S96" s="3" t="inlineStr"/>
+      <c r="T96" s="5" t="inlineStr"/>
+      <c r="U96" s="3" t="inlineStr"/>
+      <c r="V96" s="5" t="inlineStr"/>
+      <c r="W96" s="5" t="inlineStr"/>
+      <c r="X96" s="5" t="inlineStr"/>
+      <c r="Y96" s="5" t="inlineStr"/>
+      <c r="Z96" s="5" t="inlineStr"/>
+      <c r="AA96" s="5" t="inlineStr"/>
+      <c r="AB96" s="5" t="inlineStr"/>
+      <c r="AC96" s="5" t="inlineStr"/>
+      <c r="AD96" s="3" t="inlineStr"/>
+      <c r="AE96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>0.5590828796478764</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>1.6899</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>2.500100000000001</v>
+      </c>
+      <c r="J97" s="6" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="n"/>
+      <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
+      <c r="Q97" s="4" t="n"/>
+      <c r="R97" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S97" s="3" t="inlineStr"/>
+      <c r="T97" s="5" t="inlineStr"/>
+      <c r="U97" s="3" t="inlineStr"/>
+      <c r="V97" s="5" t="inlineStr"/>
+      <c r="W97" s="5" t="inlineStr"/>
+      <c r="X97" s="5" t="inlineStr"/>
+      <c r="Y97" s="5" t="inlineStr"/>
+      <c r="Z97" s="5" t="inlineStr"/>
+      <c r="AA97" s="5" t="inlineStr"/>
+      <c r="AB97" s="5" t="inlineStr"/>
+      <c r="AC97" s="5" t="inlineStr"/>
+      <c r="AD97" s="3" t="inlineStr"/>
+      <c r="AE97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>1.379517548940123</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>1.6864</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>2.4636</v>
+      </c>
+      <c r="J98" s="6" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="n"/>
+      <c r="O98" s="4" t="n"/>
+      <c r="P98" s="4" t="n"/>
+      <c r="Q98" s="4" t="n"/>
+      <c r="R98" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S98" s="3" t="inlineStr"/>
+      <c r="T98" s="5" t="inlineStr"/>
+      <c r="U98" s="3" t="inlineStr"/>
+      <c r="V98" s="5" t="inlineStr"/>
+      <c r="W98" s="5" t="inlineStr"/>
+      <c r="X98" s="5" t="inlineStr"/>
+      <c r="Y98" s="5" t="inlineStr"/>
+      <c r="Z98" s="5" t="inlineStr"/>
+      <c r="AA98" s="5" t="inlineStr"/>
+      <c r="AB98" s="5" t="inlineStr"/>
+      <c r="AC98" s="5" t="inlineStr"/>
+      <c r="AD98" s="3" t="inlineStr"/>
+      <c r="AE98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>1.379517548940123</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>1.6864</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>2.4636</v>
+      </c>
+      <c r="J99" s="6" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="n"/>
+      <c r="O99" s="4" t="n"/>
+      <c r="P99" s="4" t="n"/>
+      <c r="Q99" s="4" t="n"/>
+      <c r="R99" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S99" s="3" t="inlineStr"/>
+      <c r="T99" s="5" t="inlineStr"/>
+      <c r="U99" s="3" t="inlineStr"/>
+      <c r="V99" s="5" t="inlineStr"/>
+      <c r="W99" s="5" t="inlineStr"/>
+      <c r="X99" s="5" t="inlineStr"/>
+      <c r="Y99" s="5" t="inlineStr"/>
+      <c r="Z99" s="5" t="inlineStr"/>
+      <c r="AA99" s="5" t="inlineStr"/>
+      <c r="AB99" s="5" t="inlineStr"/>
+      <c r="AC99" s="5" t="inlineStr"/>
+      <c r="AD99" s="3" t="inlineStr"/>
+      <c r="AE99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>1.379517548940123</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>1.6864</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>2.4636</v>
+      </c>
+      <c r="J100" s="6" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="n"/>
+      <c r="O100" s="4" t="n"/>
+      <c r="P100" s="4" t="n"/>
+      <c r="Q100" s="4" t="n"/>
+      <c r="R100" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S100" s="3" t="inlineStr"/>
+      <c r="T100" s="5" t="inlineStr"/>
+      <c r="U100" s="3" t="inlineStr"/>
+      <c r="V100" s="5" t="inlineStr"/>
+      <c r="W100" s="5" t="inlineStr"/>
+      <c r="X100" s="5" t="inlineStr"/>
+      <c r="Y100" s="5" t="inlineStr"/>
+      <c r="Z100" s="5" t="inlineStr"/>
+      <c r="AA100" s="5" t="inlineStr"/>
+      <c r="AB100" s="5" t="inlineStr"/>
+      <c r="AC100" s="5" t="inlineStr"/>
+      <c r="AD100" s="3" t="inlineStr"/>
+      <c r="AE100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>1.696795725703693</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>1.6722</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>2.4678</v>
+      </c>
+      <c r="J101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="n"/>
+      <c r="O101" s="4" t="n"/>
+      <c r="P101" s="4" t="n"/>
+      <c r="Q101" s="4" t="n"/>
+      <c r="R101" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+      <c r="S101" s="3" t="inlineStr"/>
+      <c r="T101" s="5" t="inlineStr"/>
+      <c r="U101" s="3" t="inlineStr"/>
+      <c r="V101" s="5" t="inlineStr"/>
+      <c r="W101" s="5" t="inlineStr"/>
+      <c r="X101" s="5" t="inlineStr"/>
+      <c r="Y101" s="5" t="inlineStr"/>
+      <c r="Z101" s="5" t="inlineStr"/>
+      <c r="AA101" s="5" t="inlineStr"/>
+      <c r="AB101" s="5" t="inlineStr"/>
+      <c r="AC101" s="5" t="inlineStr"/>
+      <c r="AD101" s="3" t="inlineStr"/>
+      <c r="AE101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>1.990002027105287</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>1.6654</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>2.4646</v>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="inlineStr">
+        <is>
+          <t>吸引力偏弱</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="P102" s="4" t="inlineStr">
+        <is>
+          <t>35.83</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="R102" s="7" t="inlineStr">
+        <is>
+          <t>中证官方指数推算</t>
+        </is>
+      </c>
+      <c r="S102" s="3" t="inlineStr">
+        <is>
+          <t>dividend-weighted-v1</t>
+        </is>
+      </c>
+      <c r="T102" s="5" t="n">
+        <v>38.07892932796965</v>
+      </c>
+      <c r="U102" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V102" s="5" t="n">
+        <v>38.07892932796965</v>
+      </c>
+      <c r="W102" s="5" t="n">
+        <v>38.07892932796965</v>
+      </c>
+      <c r="X102" s="5" t="n">
+        <v>28.665568369028</v>
+      </c>
+      <c r="Y102" s="5" t="n">
+        <v>42.59999999999999</v>
+      </c>
+      <c r="Z102" s="5" t="n">
+        <v>49.59769424762819</v>
+      </c>
+      <c r="AA102" s="5" t="n">
+        <v>12.8995057660626</v>
+      </c>
+      <c r="AB102" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AC102" s="5" t="n">
+        <v>12.39942356190705</v>
+      </c>
+      <c r="AD102" s="3" t="inlineStr">
+        <is>
+          <t>参考评分</t>
+        </is>
+      </c>
+      <c r="AE102" s="3" t="inlineStr">
+        <is>
+          <t>待确认 D：1/3个交易日</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R88"/>
+  <autoFilter ref="A1:AE102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -879,22 +879,22 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T3" s="5" t="n">
-        <v>66.20371132950213</v>
+        <v>58.68651044846207</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V3" s="5" t="n">
-        <v>66.20371132950213</v>
+        <v>58.68651044846207</v>
       </c>
       <c r="W3" s="5" t="n">
-        <v>66.20371132950213</v>
+        <v>58.68651044846207</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>59.62077493816983</v>
@@ -945,22 +945,22 @@
         <v>82.681380605776</v>
       </c>
       <c r="AA3" s="5" t="n">
-        <v>19.67485572959605</v>
+        <v>2.9810387469084914</v>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>19.244</v>
+        <v>52.071999999999996</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>27.28485559990608</v>
+        <v>6.61451044846208</v>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1000,22 +1000,22 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr">
@@ -1039,22 +1039,22 @@
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T4" s="10" t="n">
-        <v>65.60579959977406</v>
+        <v>58.67676412891172</v>
       </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V4" s="10" t="n">
-        <v>65.60579959977406</v>
+        <v>58.67676412891172</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>65.60579959977406</v>
+        <v>58.67676412891172</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>57.93075020610058</v>
@@ -1066,22 +1066,22 @@
         <v>82.55955161139654</v>
       </c>
       <c r="AA4" s="10" t="n">
-        <v>19.11714756801319</v>
+        <v>2.8965375103050293</v>
       </c>
       <c r="AB4" s="10" t="n">
-        <v>19.244</v>
+        <v>52.071999999999996</v>
       </c>
       <c r="AC4" s="10" t="n">
-        <v>27.24465203176086</v>
+        <v>6.604764128911723</v>
       </c>
       <c r="AD4" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE4" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N5" s="8" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="S5" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T5" s="10" t="n">
-        <v>65.78395924197142</v>
+        <v>59.05722381593583</v>
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V5" s="10" t="n">
-        <v>65.78395924197142</v>
+        <v>59.05722381593583</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>65.78395924197142</v>
+        <v>59.05722381593583</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>57.90276060980635</v>
@@ -1187,22 +1187,22 @@
         <v>82.71529769919793</v>
       </c>
       <c r="AA5" s="10" t="n">
-        <v>19.1079110012361</v>
+        <v>2.8951380304903176</v>
       </c>
       <c r="AB5" s="10" t="n">
-        <v>19.38</v>
+        <v>52.43999999999999</v>
       </c>
       <c r="AC5" s="10" t="n">
-        <v>27.29604824073532</v>
+        <v>6.6172238159358345</v>
       </c>
       <c r="AD5" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE5" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1236,22 +1236,22 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
@@ -1275,25 +1275,25 @@
       </c>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T6" s="10" t="n">
-        <v>65.75815419783031</v>
+        <v>59.975340086830684</v>
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V6" s="10" t="n">
-        <v>65.75815419783031</v>
+        <v>59.975340086830684</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>65.75815419783031</v>
+        <v>59.975340086830684</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>56.81780708985985</v>
+        <v>56.817807089859855</v>
       </c>
       <c r="Y6" s="10" t="n">
         <v>58.00000000000001</v>
@@ -1302,22 +1302,22 @@
         <v>82.6917510853835</v>
       </c>
       <c r="AA6" s="10" t="n">
-        <v>18.74987633965375</v>
+        <v>2.8408903544929927</v>
       </c>
       <c r="AB6" s="10" t="n">
-        <v>19.72</v>
+        <v>53.36000000000001</v>
       </c>
       <c r="AC6" s="10" t="n">
-        <v>27.28827785817656</v>
+        <v>6.61534008683068</v>
       </c>
       <c r="AD6" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE6" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1351,22 +1351,22 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T7" s="10" t="n">
-        <v>64.18267474339099</v>
+        <v>59.964788213628</v>
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V7" s="10" t="n">
-        <v>64.18267474339099</v>
+        <v>59.964788213628</v>
       </c>
       <c r="W7" s="10" t="n">
-        <v>64.18267474339099</v>
+        <v>59.964788213628</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>52.17552533992583</v>
@@ -1417,22 +1417,22 @@
         <v>82.55985267034991</v>
       </c>
       <c r="AA7" s="10" t="n">
-        <v>17.21792336217552</v>
+        <v>2.608776266996291</v>
       </c>
       <c r="AB7" s="10" t="n">
-        <v>19.72</v>
+        <v>53.36000000000001</v>
       </c>
       <c r="AC7" s="10" t="n">
-        <v>27.24475138121547</v>
+        <v>6.604788213627993</v>
       </c>
       <c r="AD7" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE7" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1466,22 +1466,22 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
@@ -1505,49 +1505,49 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T8" s="10" t="n">
-        <v>64.89741809883397</v>
+        <v>60.51744747081712</v>
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V8" s="10" t="n">
-        <v>64.89741809883397</v>
+        <v>60.51744747081712</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>64.89741809883397</v>
+        <v>60.51744747081712</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>53.71499176276772</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>58.59999999999999</v>
+        <v>58.599999999999994</v>
       </c>
       <c r="Z8" s="10" t="n">
         <v>82.56809338521401</v>
       </c>
       <c r="AA8" s="10" t="n">
-        <v>17.72594728171335</v>
+        <v>2.685749588138386</v>
       </c>
       <c r="AB8" s="10" t="n">
-        <v>19.924</v>
+        <v>53.912</v>
       </c>
       <c r="AC8" s="10" t="n">
-        <v>27.24747081712063</v>
+        <v>6.605447470817121</v>
       </c>
       <c r="AD8" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE8" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
@@ -1620,49 +1620,49 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T9" s="10" t="n">
-        <v>64.77010006060532</v>
+        <v>60.89287553648069</v>
       </c>
       <c r="U9" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V9" s="10" t="n">
-        <v>64.77010006060532</v>
+        <v>60.89287553648069</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>64.77010006060532</v>
+        <v>60.89287553648069</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>52.8242074927954</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>59</v>
+        <v>59.0</v>
       </c>
       <c r="Z9" s="10" t="n">
         <v>82.66094420600858</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>17.43198847262248</v>
+        <v>2.6412103746397704</v>
       </c>
       <c r="AB9" s="10" t="n">
-        <v>20.06</v>
+        <v>54.28</v>
       </c>
       <c r="AC9" s="10" t="n">
-        <v>27.27811158798283</v>
+        <v>6.612875536480686</v>
       </c>
       <c r="AD9" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE9" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1696,22 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
@@ -1735,49 +1735,49 @@
       </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T10" s="10" t="n">
-        <v>63.57543198400099</v>
+        <v>59.58416158833993</v>
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V10" s="10" t="n">
-        <v>63.57543198400099</v>
+        <v>59.58416158833993</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>63.57543198400099</v>
+        <v>59.58416158833993</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>50.90534979423868</v>
       </c>
       <c r="Y10" s="10" t="n">
-        <v>57.59999999999999</v>
+        <v>57.599999999999994</v>
       </c>
       <c r="Z10" s="10" t="n">
         <v>82.40201985424915</v>
       </c>
       <c r="AA10" s="10" t="n">
-        <v>16.79876543209877</v>
+        <v>2.545267489711934</v>
       </c>
       <c r="AB10" s="10" t="n">
-        <v>19.584</v>
+        <v>52.992</v>
       </c>
       <c r="AC10" s="10" t="n">
-        <v>27.19266655190222</v>
+        <v>6.592161588339931</v>
       </c>
       <c r="AD10" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE10" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1811,22 +1811,22 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
@@ -1850,22 +1850,22 @@
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T11" s="10" t="n">
-        <v>63.10417633420911</v>
+        <v>62.96223135534519</v>
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V11" s="10" t="n">
-        <v>63.10417633420911</v>
+        <v>62.96223135534519</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>63.10417633420911</v>
+        <v>62.96223135534519</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>44.94233937397035</v>
@@ -1877,22 +1877,22 @@
         <v>83.22789194181482</v>
       </c>
       <c r="AA11" s="10" t="n">
-        <v>14.83097199341021</v>
+        <v>2.2471169686985175</v>
       </c>
       <c r="AB11" s="10" t="n">
-        <v>20.808</v>
+        <v>56.304</v>
       </c>
       <c r="AC11" s="10" t="n">
-        <v>27.46520434079889</v>
+        <v>6.658231355345185</v>
       </c>
       <c r="AD11" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE11" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -1926,22 +1926,22 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T12" s="10" t="n">
-        <v>65.02625748433877</v>
+        <v>64.82657093225247</v>
       </c>
       <c r="U12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V12" s="10" t="n">
-        <v>65.02625748433877</v>
+        <v>64.82657093225247</v>
       </c>
       <c r="W12" s="10" t="n">
-        <v>65.02625748433877</v>
+        <v>64.82657093225247</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>48.40197693574959</v>
@@ -1992,22 +1992,22 @@
         <v>83.53213665315576</v>
       </c>
       <c r="AA12" s="10" t="n">
-        <v>15.97265238879736</v>
+        <v>2.4200988467874796</v>
       </c>
       <c r="AB12" s="10" t="n">
-        <v>21.488</v>
+        <v>58.144000000000005</v>
       </c>
       <c r="AC12" s="10" t="n">
-        <v>27.5656050955414</v>
+        <v>6.682570932252461</v>
       </c>
       <c r="AD12" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE12" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2080,22 +2080,22 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T13" s="5" t="n">
-        <v>67.00882176570842</v>
+        <v>68.91211098907455</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V13" s="5" t="n">
-        <v>67.00882176570842</v>
+        <v>68.91211098907455</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>67.00882176570842</v>
+        <v>68.91211098907455</v>
       </c>
       <c r="X13" s="5" t="n">
         <v>49.40716344174557</v>
@@ -2107,22 +2107,22 @@
         <v>84.00138736343142</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>16.30436393577604</v>
+        <v>2.4703581720872787</v>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>22.98400000000001</v>
+        <v>62.19200000000003</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>27.72045782993237</v>
+        <v>6.720110989074514</v>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2156,22 +2156,22 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
@@ -2195,49 +2195,49 @@
       </c>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T14" s="10" t="n">
-        <v>65.82644988483872</v>
+        <v>67.04529496402877</v>
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V14" s="10" t="n">
-        <v>65.82644988483872</v>
+        <v>67.04529496402877</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>65.82644988483872</v>
+        <v>67.04529496402877</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>48.22002472187886</v>
       </c>
       <c r="Y14" s="10" t="n">
-        <v>65.59999999999999</v>
+        <v>65.6</v>
       </c>
       <c r="Z14" s="10" t="n">
         <v>83.66618705035971</v>
       </c>
       <c r="AA14" s="10" t="n">
-        <v>15.91260815822002</v>
+        <v>2.4110012360939432</v>
       </c>
       <c r="AB14" s="10" t="n">
-        <v>22.30399999999999</v>
+        <v>60.352</v>
       </c>
       <c r="AC14" s="10" t="n">
-        <v>27.60984172661871</v>
+        <v>6.693294964028777</v>
       </c>
       <c r="AD14" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE14" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2271,22 +2271,22 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T15" s="10" t="n">
-        <v>65.8985785519376</v>
+        <v>68.15357412398922</v>
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V15" s="10" t="n">
-        <v>65.8985785519376</v>
+        <v>68.15357412398922</v>
       </c>
       <c r="W15" s="10" t="n">
-        <v>65.8985785519376</v>
+        <v>68.15357412398922</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>47.14874330449115</v>
@@ -2337,22 +2337,22 @@
         <v>83.71967654986523</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>15.55908529048208</v>
+        <v>2.3574371652245576</v>
       </c>
       <c r="AB15" s="10" t="n">
-        <v>22.712</v>
+        <v>61.455999999999996</v>
       </c>
       <c r="AC15" s="10" t="n">
-        <v>27.62749326145552</v>
+        <v>6.697574123989218</v>
       </c>
       <c r="AD15" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE15" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2425,49 +2425,49 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T16" s="5" t="n">
-        <v>66.29773347367043</v>
+        <v>71.12506015812994</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V16" s="5" t="n">
-        <v>66.29773347367043</v>
+        <v>71.12506015812994</v>
       </c>
       <c r="W16" s="5" t="n">
-        <v>66.29773347367043</v>
+        <v>71.12506015812994</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>44.71775854964977</v>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="Z16" s="5" t="n">
         <v>84.06325197662427</v>
       </c>
       <c r="AA16" s="5" t="n">
-        <v>14.75686032138442</v>
+        <v>2.2358879274824885</v>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>23.8</v>
+        <v>64.4</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>27.74087315228601</v>
+        <v>6.725060158129942</v>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2501,22 +2501,22 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
@@ -2540,22 +2540,22 @@
       </c>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T17" s="10" t="n">
-        <v>64.53187709789265</v>
+        <v>73.36661909976368</v>
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V17" s="10" t="n">
-        <v>64.53187709789265</v>
+        <v>73.36661909976368</v>
       </c>
       <c r="W17" s="10" t="n">
-        <v>64.53187709789265</v>
+        <v>73.36661909976368</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>36.47446457990115</v>
@@ -2567,22 +2567,22 @@
         <v>84.48273874704628</v>
       </c>
       <c r="AA17" s="10" t="n">
-        <v>12.03657331136738</v>
+        <v>1.8237232289950578</v>
       </c>
       <c r="AB17" s="10" t="n">
-        <v>24.616</v>
+        <v>66.60799999999998</v>
       </c>
       <c r="AC17" s="10" t="n">
-        <v>27.87930378652527</v>
+        <v>6.758619099763703</v>
       </c>
       <c r="AD17" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE17" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2616,22 +2616,22 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2655,22 +2655,22 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T18" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V18" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="W18" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>48.74845615479622</v>
@@ -2682,22 +2682,22 @@
         <v>85.08952292942128</v>
       </c>
       <c r="AA18" s="5" t="n">
-        <v>16.08699053108275</v>
+        <v>2.4374228077398112</v>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>26.248</v>
+        <v>71.02399999999999</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>28.07954256670902</v>
+        <v>6.807161834353702</v>
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2770,22 +2770,22 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T19" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V19" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="X19" s="5" t="n">
         <v>48.74845615479622</v>
@@ -2797,22 +2797,22 @@
         <v>85.08952292942128</v>
       </c>
       <c r="AA19" s="5" t="n">
-        <v>16.08699053108275</v>
+        <v>2.4374228077398112</v>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>26.248</v>
+        <v>71.02399999999999</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>28.07954256670902</v>
+        <v>6.807161834353702</v>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2846,22 +2846,22 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 基础配置区间</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2885,22 +2885,22 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T20" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V20" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>70.41453309779178</v>
+        <v>77.8311618343537</v>
       </c>
       <c r="X20" s="5" t="n">
         <v>48.74845615479622</v>
@@ -2912,22 +2912,22 @@
         <v>85.08952292942128</v>
       </c>
       <c r="AA20" s="5" t="n">
-        <v>16.08699053108275</v>
+        <v>2.4374228077398112</v>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>26.248</v>
+        <v>71.02399999999999</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>28.07954256670902</v>
+        <v>6.807161834353702</v>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2961,22 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">A · 买入区间</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
@@ -3000,49 +3000,49 @@
       </c>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T21" s="10" t="n">
-        <v>65.86564379616905</v>
+        <v>76.3610856144438</v>
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="V21" s="10" t="n">
-        <v>65.86564379616905</v>
+        <v>76.3610856144438</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>65.86564379616905</v>
+        <v>76.3610856144438</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>36.58838071693449</v>
       </c>
       <c r="Y21" s="10" t="n">
-        <v>75.59999999999999</v>
+        <v>75.6</v>
       </c>
       <c r="Z21" s="10" t="n">
         <v>85.11357018054747</v>
       </c>
       <c r="AA21" s="10" t="n">
-        <v>12.07416563658838</v>
+        <v>1.8294190358467244</v>
       </c>
       <c r="AB21" s="10" t="n">
-        <v>25.704</v>
+        <v>69.55199999999999</v>
       </c>
       <c r="AC21" s="10" t="n">
-        <v>28.08747815958067</v>
+        <v>6.809085614443798</v>
       </c>
       <c r="AD21" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE21" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3076,22 +3076,22 @@
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
@@ -3115,22 +3115,22 @@
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T22" s="10" t="n">
-        <v>58.41786670299579</v>
+        <v>58.843420657818804</v>
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V22" s="10" t="n">
-        <v>58.41786670299579</v>
+        <v>58.843420657818804</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>58.41786670299579</v>
+        <v>58.843420657818804</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>36.1598681499794</v>
@@ -3142,22 +3142,22 @@
         <v>82.34275822273514</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>11.9327564894932</v>
+        <v>1.80799340749897</v>
       </c>
       <c r="AB22" s="10" t="n">
-        <v>19.312</v>
+        <v>52.25599999999999</v>
       </c>
       <c r="AC22" s="10" t="n">
-        <v>27.1731102135026</v>
+        <v>6.587420657818812</v>
       </c>
       <c r="AD22" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE22" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
@@ -3230,49 +3230,49 @@
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T23" s="10" t="n">
-        <v>56.00604754966054</v>
+        <v>57.329988078862904</v>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V23" s="10" t="n">
-        <v>56.00604754966054</v>
+        <v>57.329988078862904</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>56.00604754966054</v>
+        <v>57.329988078862904</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>31.01771734651834</v>
       </c>
       <c r="Y23" s="10" t="n">
-        <v>55.2</v>
+        <v>55.199999999999996</v>
       </c>
       <c r="Z23" s="10" t="n">
         <v>81.82485098578634</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>10.23584672435105</v>
+        <v>1.550885867325917</v>
       </c>
       <c r="AB23" s="10" t="n">
-        <v>18.768</v>
+        <v>50.784</v>
       </c>
       <c r="AC23" s="10" t="n">
-        <v>27.00220082530949</v>
+        <v>6.545988078862908</v>
       </c>
       <c r="AD23" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE23" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3306,22 +3306,22 @@
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
@@ -3345,25 +3345,25 @@
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T24" s="10" t="n">
-        <v>55.52179971176783</v>
+        <v>56.583094773118894</v>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V24" s="10" t="n">
-        <v>55.52179971176783</v>
+        <v>56.583094773118894</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>55.52179971176783</v>
+        <v>56.583094773118894</v>
       </c>
       <c r="X24" s="10" t="n">
-        <v>30.51070840197693</v>
+        <v>30.510708401976938</v>
       </c>
       <c r="Y24" s="10" t="n">
         <v>54.39999999999999</v>
@@ -3372,22 +3372,22 @@
         <v>81.68868466398621</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>10.06853377265239</v>
+        <v>1.525535420098847</v>
       </c>
       <c r="AB24" s="10" t="n">
-        <v>18.496</v>
+        <v>50.047999999999995</v>
       </c>
       <c r="AC24" s="10" t="n">
-        <v>26.95726593911545</v>
+        <v>6.535094773118897</v>
       </c>
       <c r="AD24" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE24" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3421,22 +3421,22 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
@@ -3460,25 +3460,25 @@
       </c>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T25" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V25" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="W25" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>31.22272540139976</v>
+        <v>31.222725401399757</v>
       </c>
       <c r="Y25" s="10" t="n">
         <v>53.4</v>
@@ -3487,22 +3487,22 @@
         <v>81.39380404283342</v>
       </c>
       <c r="AA25" s="10" t="n">
-        <v>10.30349938246192</v>
+        <v>1.561136270069988</v>
       </c>
       <c r="AB25" s="10" t="n">
-        <v>18.156</v>
+        <v>49.128</v>
       </c>
       <c r="AC25" s="10" t="n">
-        <v>26.85995533413503</v>
+        <v>6.511504323426674</v>
       </c>
       <c r="AD25" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE25" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3536,22 +3536,22 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
@@ -3575,25 +3575,25 @@
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T26" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V26" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="X26" s="10" t="n">
-        <v>31.22272540139976</v>
+        <v>31.222725401399757</v>
       </c>
       <c r="Y26" s="10" t="n">
         <v>53.4</v>
@@ -3602,22 +3602,22 @@
         <v>81.39380404283342</v>
       </c>
       <c r="AA26" s="10" t="n">
-        <v>10.30349938246192</v>
+        <v>1.561136270069988</v>
       </c>
       <c r="AB26" s="10" t="n">
-        <v>18.156</v>
+        <v>49.128</v>
       </c>
       <c r="AC26" s="10" t="n">
-        <v>26.85995533413503</v>
+        <v>6.511504323426674</v>
       </c>
       <c r="AD26" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE26" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
@@ -3690,25 +3690,25 @@
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T27" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V27" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>55.31945471659695</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>31.22272540139976</v>
+        <v>31.222725401399757</v>
       </c>
       <c r="Y27" s="10" t="n">
         <v>53.4</v>
@@ -3717,22 +3717,22 @@
         <v>81.39380404283342</v>
       </c>
       <c r="AA27" s="10" t="n">
-        <v>10.30349938246192</v>
+        <v>1.561136270069988</v>
       </c>
       <c r="AB27" s="10" t="n">
-        <v>18.156</v>
+        <v>49.128</v>
       </c>
       <c r="AC27" s="10" t="n">
-        <v>26.85995533413503</v>
+        <v>6.511504323426674</v>
       </c>
       <c r="AD27" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE27" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M28" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
@@ -3811,22 +3811,22 @@
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T28" s="10" t="n">
-        <v>52.19939533413503</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V28" s="10" t="n">
-        <v>52.19939533413503</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="W28" s="10" t="n">
-        <v>52.19939533413503</v>
+        <v>55.63950432342668</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>21.768</v>
@@ -3838,22 +3838,22 @@
         <v>81.39380404283342</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>7.183440000000001</v>
+        <v>1.0884</v>
       </c>
       <c r="AB28" s="10" t="n">
-        <v>18.156</v>
+        <v>49.128</v>
       </c>
       <c r="AC28" s="10" t="n">
-        <v>26.85995533413503</v>
+        <v>6.511504323426674</v>
       </c>
       <c r="AD28" s="8" t="inlineStr">
         <is>
-          <t>日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE28" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -3887,22 +3887,22 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
@@ -3926,49 +3926,49 @@
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T29" s="10" t="n">
-        <v>54.55191695104509</v>
+        <v>53.77095068761149</v>
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V29" s="10" t="n">
-        <v>54.55191695104509</v>
+        <v>53.77095068761149</v>
       </c>
       <c r="W29" s="10" t="n">
-        <v>54.55191695104509</v>
+        <v>53.77095068761149</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>31.31437989287186</v>
       </c>
       <c r="Y29" s="10" t="n">
-        <v>51.40000000000001</v>
+        <v>51.400000000000006</v>
       </c>
       <c r="Z29" s="10" t="n">
         <v>81.03688359514356</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>10.33374536464771</v>
+        <v>1.565718994643593</v>
       </c>
       <c r="AB29" s="10" t="n">
-        <v>17.476</v>
+        <v>47.288000000000004</v>
       </c>
       <c r="AC29" s="10" t="n">
-        <v>26.74217158639738</v>
+        <v>6.482950687611485</v>
       </c>
       <c r="AD29" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE29" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4002,22 +4002,22 @@
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M30" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
@@ -4041,25 +4041,25 @@
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T30" s="10" t="n">
-        <v>54.96015421475651</v>
+        <v>55.0820783637826</v>
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V30" s="10" t="n">
-        <v>54.96015421475651</v>
+        <v>55.0820783637826</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>54.96015421475651</v>
+        <v>55.0820783637826</v>
       </c>
       <c r="X30" s="10" t="n">
-        <v>30.81994231561599</v>
+        <v>30.819942315615986</v>
       </c>
       <c r="Y30" s="10" t="n">
         <v>52.8</v>
@@ -4068,22 +4068,22 @@
         <v>81.32597954728254</v>
       </c>
       <c r="AA30" s="10" t="n">
-        <v>10.17058096415328</v>
+        <v>1.5409971157807993</v>
       </c>
       <c r="AB30" s="10" t="n">
-        <v>17.952</v>
+        <v>48.57599999999999</v>
       </c>
       <c r="AC30" s="10" t="n">
-        <v>26.83757325060324</v>
+        <v>6.506078363782604</v>
       </c>
       <c r="AD30" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4117,22 +4117,22 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
@@ -4162,49 +4162,49 @@
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T31" s="10" t="n">
-        <v>50.71162319240725</v>
+        <v>54.70877653149266</v>
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V31" s="10" t="n">
-        <v>50.71162319240725</v>
+        <v>54.70877653149266</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>50.71162319240725</v>
+        <v>54.70877653149266</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>18.424</v>
       </c>
       <c r="Y31" s="10" t="n">
-        <v>52.40000000000001</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="Z31" s="10" t="n">
         <v>81.25970664365832</v>
       </c>
       <c r="AA31" s="10" t="n">
-        <v>6.07992</v>
+        <v>0.9212</v>
       </c>
       <c r="AB31" s="10" t="n">
-        <v>17.816</v>
+        <v>48.208</v>
       </c>
       <c r="AC31" s="10" t="n">
-        <v>26.81570319240724</v>
+        <v>6.500776531492665</v>
       </c>
       <c r="AD31" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE31" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4238,22 +4238,22 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M32" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
@@ -4283,25 +4283,25 @@
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T32" s="10" t="n">
-        <v>51.96018386740332</v>
+        <v>55.64807366482505</v>
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V32" s="10" t="n">
-        <v>51.96018386740332</v>
+        <v>55.64807366482505</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>51.96018386740332</v>
+        <v>55.64807366482505</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>20.936</v>
+        <v>20.936000000000003</v>
       </c>
       <c r="Y32" s="10" t="n">
         <v>53.4</v>
@@ -4310,22 +4310,22 @@
         <v>81.50092081031308</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>6.908880000000002</v>
+        <v>1.0468000000000002</v>
       </c>
       <c r="AB32" s="10" t="n">
-        <v>18.156</v>
+        <v>49.128</v>
       </c>
       <c r="AC32" s="10" t="n">
-        <v>26.89530386740331</v>
+        <v>6.520073664825046</v>
       </c>
       <c r="AD32" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE32" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4359,22 +4359,22 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
@@ -4404,22 +4404,22 @@
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T33" s="10" t="n">
-        <v>52.00932007816991</v>
+        <v>56.02125577652605</v>
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V33" s="10" t="n">
-        <v>52.00932007816991</v>
+        <v>56.02125577652605</v>
       </c>
       <c r="W33" s="10" t="n">
-        <v>52.00932007816991</v>
+        <v>56.02125577652605</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>20.608</v>
@@ -4431,22 +4431,22 @@
         <v>81.56569720657546</v>
       </c>
       <c r="AA33" s="10" t="n">
-        <v>6.80064</v>
+        <v>1.0304</v>
       </c>
       <c r="AB33" s="10" t="n">
-        <v>18.292</v>
+        <v>49.49600000000001</v>
       </c>
       <c r="AC33" s="10" t="n">
-        <v>26.9166800781699</v>
+        <v>6.525255776526037</v>
       </c>
       <c r="AD33" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE33" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4480,22 +4480,22 @@
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M34" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
@@ -4525,49 +4525,49 @@
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T34" s="10" t="n">
-        <v>50.06551133126935</v>
+        <v>55.8292342621259</v>
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V34" s="10" t="n">
-        <v>50.06551133126935</v>
+        <v>55.8292342621259</v>
       </c>
       <c r="W34" s="10" t="n">
-        <v>50.06551133126935</v>
+        <v>55.8292342621259</v>
       </c>
       <c r="X34" s="10" t="n">
-        <v>15.024</v>
+        <v>15.024000000000001</v>
       </c>
       <c r="Y34" s="10" t="n">
-        <v>53.59999999999999</v>
+        <v>53.599999999999994</v>
       </c>
       <c r="Z34" s="10" t="n">
         <v>81.46542827657379</v>
       </c>
       <c r="AA34" s="10" t="n">
-        <v>4.957920000000001</v>
+        <v>0.7512000000000001</v>
       </c>
       <c r="AB34" s="10" t="n">
-        <v>18.224</v>
+        <v>49.312</v>
       </c>
       <c r="AC34" s="10" t="n">
-        <v>26.88359133126935</v>
+        <v>6.517234262125903</v>
       </c>
       <c r="AD34" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE34" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T35" s="10" t="n">
-        <v>48.45016687737042</v>
+        <v>53.95640409148374</v>
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V35" s="10" t="n">
-        <v>48.45016687737042</v>
+        <v>53.95640409148374</v>
       </c>
       <c r="W35" s="10" t="n">
-        <v>48.45016687737042</v>
+        <v>53.95640409148374</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>12.6</v>
@@ -4673,22 +4673,22 @@
         <v>81.05505114354672</v>
       </c>
       <c r="AA35" s="10" t="n">
-        <v>4.158</v>
+        <v>0.63</v>
       </c>
       <c r="AB35" s="10" t="n">
-        <v>17.544</v>
+        <v>47.472</v>
       </c>
       <c r="AC35" s="10" t="n">
-        <v>26.74816687737042</v>
+        <v>6.4844040914837375</v>
       </c>
       <c r="AD35" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE35" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4722,22 +4722,22 @@
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M36" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T36" s="10" t="n">
-        <v>54.10355715709471</v>
+        <v>52.829955647477874</v>
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V36" s="10" t="n">
-        <v>54.10355715709471</v>
+        <v>52.829955647477874</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>54.10355715709471</v>
+        <v>52.829955647477874</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>31.24845488257108</v>
@@ -4788,22 +4788,22 @@
         <v>80.77444559347352</v>
       </c>
       <c r="AA36" s="10" t="n">
-        <v>10.31199011124846</v>
+        <v>1.562422744128554</v>
       </c>
       <c r="AB36" s="10" t="n">
-        <v>17.136</v>
+        <v>46.367999999999995</v>
       </c>
       <c r="AC36" s="10" t="n">
-        <v>26.65556704584626</v>
+        <v>6.461955647477882</v>
       </c>
       <c r="AD36" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE36" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4837,22 +4837,22 @@
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
@@ -4882,49 +4882,49 @@
       </c>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T37" s="10" t="n">
-        <v>49.1767601169926</v>
+        <v>53.765352755634574</v>
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V37" s="10" t="n">
-        <v>49.1767601169926</v>
+        <v>53.765352755634574</v>
       </c>
       <c r="W37" s="10" t="n">
-        <v>49.1767601169926</v>
+        <v>53.765352755634574</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>15.096</v>
       </c>
       <c r="Y37" s="10" t="n">
-        <v>51.40000000000001</v>
+        <v>51.400000000000006</v>
       </c>
       <c r="Z37" s="10" t="n">
         <v>80.96690944543212</v>
       </c>
       <c r="AA37" s="10" t="n">
-        <v>4.98168</v>
+        <v>0.7548</v>
       </c>
       <c r="AB37" s="10" t="n">
-        <v>17.476</v>
+        <v>47.288000000000004</v>
       </c>
       <c r="AC37" s="10" t="n">
-        <v>26.7190801169926</v>
+        <v>6.47735275563457</v>
       </c>
       <c r="AD37" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE37" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -4958,22 +4958,22 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M38" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
@@ -5003,22 +5003,22 @@
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T38" s="10" t="n">
-        <v>47.69434627441967</v>
+        <v>54.331565157435065</v>
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V38" s="10" t="n">
-        <v>47.69434627441967</v>
+        <v>54.331565157435065</v>
       </c>
       <c r="W38" s="10" t="n">
-        <v>47.69434627441967</v>
+        <v>54.331565157435065</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>9.808</v>
@@ -5030,22 +5030,22 @@
         <v>81.14456446793841</v>
       </c>
       <c r="AA38" s="10" t="n">
-        <v>3.23664</v>
+        <v>0.4904</v>
       </c>
       <c r="AB38" s="10" t="n">
-        <v>17.68</v>
+        <v>47.83999999999999</v>
       </c>
       <c r="AC38" s="10" t="n">
-        <v>26.77770627441967</v>
+        <v>6.491565157435073</v>
       </c>
       <c r="AD38" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE38" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5079,22 +5079,22 @@
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
@@ -5118,22 +5118,22 @@
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T39" s="10" t="n">
-        <v>53.42317304359078</v>
+        <v>51.69947814129377</v>
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V39" s="10" t="n">
-        <v>53.42317304359078</v>
+        <v>51.69947814129377</v>
       </c>
       <c r="W39" s="10" t="n">
-        <v>53.42317304359078</v>
+        <v>51.69947814129377</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>30.75401730531521</v>
@@ -5145,22 +5145,22 @@
         <v>80.44347676617201</v>
       </c>
       <c r="AA39" s="10" t="n">
-        <v>10.14882571075402</v>
+        <v>1.5377008652657604</v>
       </c>
       <c r="AB39" s="10" t="n">
-        <v>16.728</v>
+        <v>45.264</v>
       </c>
       <c r="AC39" s="10" t="n">
-        <v>26.54634733283676</v>
+        <v>6.4354781412937605</v>
       </c>
       <c r="AD39" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE39" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5194,22 +5194,22 @@
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
@@ -5233,25 +5233,25 @@
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T40" s="10" t="n">
-        <v>51.24322660924289</v>
+        <v>51.714228363299995</v>
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V40" s="10" t="n">
-        <v>51.24322660924289</v>
+        <v>51.714228363299995</v>
       </c>
       <c r="W40" s="10" t="n">
-        <v>51.24322660924289</v>
+        <v>51.714228363299995</v>
       </c>
       <c r="X40" s="10" t="n">
-        <v>23.96374124433457</v>
+        <v>23.963741244334567</v>
       </c>
       <c r="Y40" s="10" t="n">
         <v>49.2</v>
@@ -5260,22 +5260,22 @@
         <v>80.62785454124993</v>
       </c>
       <c r="AA40" s="10" t="n">
-        <v>7.908034610630408</v>
+        <v>1.1981870622167283</v>
       </c>
       <c r="AB40" s="10" t="n">
-        <v>16.728</v>
+        <v>45.264</v>
       </c>
       <c r="AC40" s="10" t="n">
-        <v>26.60719199861248</v>
+        <v>6.450228363299995</v>
       </c>
       <c r="AD40" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE40" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5309,22 +5309,22 @@
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
@@ -5354,22 +5354,22 @@
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T41" s="10" t="n">
-        <v>44.21744</v>
+        <v>50.77309090909092</v>
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V41" s="10" t="n">
-        <v>44.21744</v>
+        <v>50.77309090909092</v>
       </c>
       <c r="W41" s="10" t="n">
-        <v>44.21744</v>
+        <v>50.77309090909092</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>3.968</v>
@@ -5381,22 +5381,22 @@
         <v>80.36363636363637</v>
       </c>
       <c r="AA41" s="10" t="n">
-        <v>1.30944</v>
+        <v>0.1984</v>
       </c>
       <c r="AB41" s="10" t="n">
-        <v>16.388</v>
+        <v>44.34400000000001</v>
       </c>
       <c r="AC41" s="10" t="n">
-        <v>26.52</v>
+        <v>6.42909090909091</v>
       </c>
       <c r="AD41" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE41" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5430,22 +5430,22 @@
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M42" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
@@ -5469,49 +5469,49 @@
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T42" s="10" t="n">
-        <v>53.5864316285077</v>
+        <v>52.466473787756044</v>
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V42" s="10" t="n">
-        <v>53.5864316285077</v>
+        <v>52.466473787756044</v>
       </c>
       <c r="W42" s="10" t="n">
-        <v>53.5864316285077</v>
+        <v>52.466473787756044</v>
       </c>
       <c r="X42" s="10" t="n">
-        <v>30.0370522848909</v>
+        <v>30.037052284890894</v>
       </c>
       <c r="Y42" s="10" t="n">
-        <v>50</v>
+        <v>50.0</v>
       </c>
       <c r="Z42" s="10" t="n">
         <v>80.83092234695059</v>
       </c>
       <c r="AA42" s="10" t="n">
-        <v>9.912227254013997</v>
+        <v>1.5018526142445447</v>
       </c>
       <c r="AB42" s="10" t="n">
-        <v>17</v>
+        <v>46.0</v>
       </c>
       <c r="AC42" s="10" t="n">
-        <v>26.67420437449369</v>
+        <v>6.466473787756047</v>
       </c>
       <c r="AD42" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE42" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
@@ -5584,25 +5584,25 @@
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T43" s="10" t="n">
-        <v>53.0294135935255</v>
+        <v>51.89811247620695</v>
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V43" s="10" t="n">
-        <v>53.0294135935255</v>
+        <v>51.89811247620695</v>
       </c>
       <c r="W43" s="10" t="n">
-        <v>53.0294135935255</v>
+        <v>51.89811247620695</v>
       </c>
       <c r="X43" s="10" t="n">
-        <v>29.17181705809642</v>
+        <v>29.171817058096416</v>
       </c>
       <c r="Y43" s="10" t="n">
         <v>49.39999999999999</v>
@@ -5611,22 +5611,22 @@
         <v>80.62640595258695</v>
       </c>
       <c r="AA43" s="10" t="n">
-        <v>9.626699629171817</v>
+        <v>1.4585908529048208</v>
       </c>
       <c r="AB43" s="10" t="n">
-        <v>16.796</v>
+        <v>45.44799999999999</v>
       </c>
       <c r="AC43" s="10" t="n">
-        <v>26.60671396435369</v>
+        <v>6.450112476206956</v>
       </c>
       <c r="AD43" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE43" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5660,22 +5660,22 @@
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M44" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
@@ -5705,25 +5705,25 @@
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T44" s="10" t="n">
-        <v>44.01498183159472</v>
+        <v>51.89678105008356</v>
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V44" s="10" t="n">
-        <v>44.01498183159472</v>
+        <v>51.89678105008356</v>
       </c>
       <c r="W44" s="10" t="n">
-        <v>44.01498183159472</v>
+        <v>51.89678105008356</v>
       </c>
       <c r="X44" s="10" t="n">
-        <v>1.872</v>
+        <v>1.8719999999999999</v>
       </c>
       <c r="Y44" s="10" t="n">
         <v>49.39999999999999</v>
@@ -5732,22 +5732,22 @@
         <v>80.60976312604461</v>
       </c>
       <c r="AA44" s="10" t="n">
-        <v>0.61776</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="AB44" s="10" t="n">
-        <v>16.796</v>
+        <v>45.44799999999999</v>
       </c>
       <c r="AC44" s="10" t="n">
-        <v>26.60122183159472</v>
+        <v>6.448781050083569</v>
       </c>
       <c r="AD44" s="8" t="inlineStr">
         <is>
-          <t>日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE44" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5781,22 +5781,22 @@
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 指标得分较高</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
@@ -5826,25 +5826,25 @@
       </c>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T45" s="10" t="n">
-        <v>43.44097426510474</v>
+        <v>50.5850216400254</v>
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V45" s="10" t="n">
-        <v>43.44097426510474</v>
+        <v>50.5850216400254</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>43.44097426510474</v>
+        <v>50.5850216400254</v>
       </c>
       <c r="X45" s="10" t="n">
-        <v>1.872</v>
+        <v>1.8719999999999999</v>
       </c>
       <c r="Y45" s="10" t="n">
         <v>48.00000000000001</v>
@@ -5853,22 +5853,22 @@
         <v>80.31277050031738</v>
       </c>
       <c r="AA45" s="10" t="n">
-        <v>0.61776</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="AB45" s="10" t="n">
-        <v>16.32</v>
+        <v>44.16000000000001</v>
       </c>
       <c r="AC45" s="10" t="n">
-        <v>26.50321426510474</v>
+        <v>6.425021640025391</v>
       </c>
       <c r="AD45" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE45" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -5902,22 +5902,22 @@
       </c>
       <c r="J46" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M46" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
@@ -5947,25 +5947,25 @@
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T46" s="10" t="n">
-        <v>42.57860968597349</v>
+        <v>49.8467029541754</v>
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V46" s="10" t="n">
-        <v>42.57860968597349</v>
+        <v>49.8467029541754</v>
       </c>
       <c r="W46" s="10" t="n">
-        <v>42.57860968597349</v>
+        <v>49.8467029541754</v>
       </c>
       <c r="X46" s="10" t="n">
-        <v>0.112</v>
+        <v>0.11200000000000002</v>
       </c>
       <c r="Y46" s="10" t="n">
         <v>47.2</v>
@@ -5974,22 +5974,22 @@
         <v>80.28378692719237</v>
       </c>
       <c r="AA46" s="10" t="n">
-        <v>0.03696000000000001</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="AB46" s="10" t="n">
-        <v>16.048</v>
+        <v>43.42400000000001</v>
       </c>
       <c r="AC46" s="10" t="n">
-        <v>26.49364968597348</v>
+        <v>6.4227029541753895</v>
       </c>
       <c r="AD46" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE46" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6023,22 +6023,22 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
@@ -6062,22 +6062,22 @@
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T47" s="10" t="n">
-        <v>49.60810399464746</v>
+        <v>45.707505979814485</v>
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V47" s="10" t="n">
-        <v>49.60810399464746</v>
+        <v>45.707505979814485</v>
       </c>
       <c r="W47" s="10" t="n">
-        <v>49.60810399464746</v>
+        <v>45.707505979814485</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>29.18073281185673</v>
@@ -6089,22 +6089,22 @@
         <v>76.84382474768101</v>
       </c>
       <c r="AA47" s="10" t="n">
-        <v>9.629641827912721</v>
+        <v>1.4590366405928363</v>
       </c>
       <c r="AB47" s="10" t="n">
-        <v>14.62</v>
+        <v>39.56</v>
       </c>
       <c r="AC47" s="10" t="n">
-        <v>25.35846216673474</v>
+        <v>6.147505979814481</v>
       </c>
       <c r="AD47" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE47" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6138,22 +6138,22 @@
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
@@ -6177,25 +6177,25 @@
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T48" s="10" t="n">
-        <v>48.17505747221273</v>
+        <v>45.89750923175491</v>
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V48" s="10" t="n">
-        <v>48.17505747221273</v>
+        <v>45.89750923175491</v>
       </c>
       <c r="W48" s="10" t="n">
-        <v>48.17505747221273</v>
+        <v>45.89750923175491</v>
       </c>
       <c r="X48" s="10" t="n">
-        <v>24.55706633704161</v>
+        <v>24.55706633704162</v>
       </c>
       <c r="Y48" s="10" t="n">
         <v>43.2</v>
@@ -6204,22 +6204,22 @@
         <v>76.91886539693634</v>
       </c>
       <c r="AA48" s="10" t="n">
-        <v>8.103831891223733</v>
+        <v>1.2278533168520809</v>
       </c>
       <c r="AB48" s="10" t="n">
-        <v>14.688</v>
+        <v>39.744</v>
       </c>
       <c r="AC48" s="10" t="n">
-        <v>25.38322558098899</v>
+        <v>6.153509231754907</v>
       </c>
       <c r="AD48" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE48" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6253,22 +6253,22 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T49" s="10" t="n">
-        <v>43.24473967534743</v>
+        <v>47.33577204250848</v>
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V49" s="10" t="n">
-        <v>43.24473967534743</v>
+        <v>47.33577204250848</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>43.24473967534743</v>
+        <v>47.33577204250848</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>6.296</v>
@@ -6325,22 +6325,22 @@
         <v>78.79715053135585</v>
       </c>
       <c r="AA49" s="10" t="n">
-        <v>2.07768</v>
+        <v>0.3148</v>
       </c>
       <c r="AB49" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC49" s="10" t="n">
-        <v>26.00305967534743</v>
+        <v>6.303772042508468</v>
       </c>
       <c r="AD49" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE49" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6374,22 +6374,22 @@
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
@@ -6419,49 +6419,49 @@
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T50" s="10" t="n">
-        <v>44.02091854583649</v>
+        <v>47.53337176868764</v>
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V50" s="10" t="n">
-        <v>44.02091854583649</v>
+        <v>47.53337176868764</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>44.02091854583649</v>
+        <v>47.53337176868764</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>8.271999999999998</v>
       </c>
       <c r="Y50" s="10" t="n">
-        <v>44.8</v>
+        <v>44.800000000000004</v>
       </c>
       <c r="Z50" s="10" t="n">
         <v>78.96714710859544</v>
       </c>
       <c r="AA50" s="10" t="n">
-        <v>2.729759999999999</v>
+        <v>0.4135999999999999</v>
       </c>
       <c r="AB50" s="10" t="n">
-        <v>15.232</v>
+        <v>41.216</v>
       </c>
       <c r="AC50" s="10" t="n">
-        <v>26.0591585458365</v>
+        <v>6.317371768687635</v>
       </c>
       <c r="AD50" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE50" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6495,22 +6495,22 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T51" s="10" t="n">
-        <v>48.65522537784454</v>
+        <v>46.517268156098716</v>
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V51" s="10" t="n">
-        <v>48.65522537784454</v>
+        <v>46.517268156098716</v>
       </c>
       <c r="W51" s="10" t="n">
-        <v>48.65522537784454</v>
+        <v>46.517268156098716</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>24.54695222405272</v>
@@ -6561,22 +6561,22 @@
         <v>77.76585195123376</v>
       </c>
       <c r="AA51" s="10" t="n">
-        <v>8.100494233937397</v>
+        <v>1.227347611202636</v>
       </c>
       <c r="AB51" s="10" t="n">
-        <v>14.892</v>
+        <v>40.296000000000014</v>
       </c>
       <c r="AC51" s="10" t="n">
-        <v>25.66273114390714</v>
+        <v>6.2212681560987</v>
       </c>
       <c r="AD51" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE51" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6610,22 +6610,22 @@
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M52" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
@@ -6649,49 +6649,49 @@
       </c>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T52" s="10" t="n">
-        <v>48.42781197917552</v>
+        <v>46.733219586303605</v>
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V52" s="10" t="n">
-        <v>48.42781197917552</v>
+        <v>46.733219586303605</v>
       </c>
       <c r="W52" s="10" t="n">
-        <v>48.42781197917552</v>
+        <v>46.733219586303605</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>23.25236722931248</v>
       </c>
       <c r="Y52" s="10" t="n">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="Z52" s="10" t="n">
         <v>78.16524482879514</v>
       </c>
       <c r="AA52" s="10" t="n">
-        <v>7.673281185673116</v>
+        <v>1.162618361465624</v>
       </c>
       <c r="AB52" s="10" t="n">
-        <v>14.96</v>
+        <v>40.48</v>
       </c>
       <c r="AC52" s="10" t="n">
-        <v>25.7945307935024</v>
+        <v>6.2532195863036115</v>
       </c>
       <c r="AD52" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE52" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
@@ -6764,22 +6764,22 @@
       </c>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T53" s="10" t="n">
-        <v>48.30950212707486</v>
+        <v>45.940649877005974</v>
       </c>
       <c r="U53" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V53" s="10" t="n">
-        <v>48.30950212707486</v>
+        <v>45.940649877005974</v>
       </c>
       <c r="W53" s="10" t="n">
-        <v>48.30950212707486</v>
+        <v>45.940649877005974</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>24.42521631644005</v>
@@ -6791,22 +6791,22 @@
         <v>77.45812346257468</v>
       </c>
       <c r="AA53" s="10" t="n">
-        <v>8.060321384425215</v>
+        <v>1.2212608158220024</v>
       </c>
       <c r="AB53" s="10" t="n">
-        <v>14.688</v>
+        <v>39.744</v>
       </c>
       <c r="AC53" s="10" t="n">
-        <v>25.56118074264964</v>
+        <v>6.196649877005974</v>
       </c>
       <c r="AD53" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE53" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6840,22 +6840,22 @@
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M54" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
@@ -6885,49 +6885,49 @@
       </c>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T54" s="10" t="n">
-        <v>42.2345324957753</v>
+        <v>46.3064175747334</v>
       </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V54" s="10" t="n">
-        <v>42.2345324957753</v>
+        <v>46.3064175747334</v>
       </c>
       <c r="W54" s="10" t="n">
-        <v>42.2345324957753</v>
+        <v>46.3064175747334</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>5.632000000000001</v>
       </c>
       <c r="Y54" s="10" t="n">
-        <v>43.59999999999999</v>
+        <v>43.599999999999994</v>
       </c>
       <c r="Z54" s="10" t="n">
         <v>77.43021968416758</v>
       </c>
       <c r="AA54" s="10" t="n">
-        <v>1.85856</v>
+        <v>0.2816</v>
       </c>
       <c r="AB54" s="10" t="n">
-        <v>14.824</v>
+        <v>40.111999999999995</v>
       </c>
       <c r="AC54" s="10" t="n">
-        <v>25.5519724957753</v>
+        <v>6.194417574733406</v>
       </c>
       <c r="AD54" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE54" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -6961,22 +6961,22 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
@@ -7000,25 +7000,25 @@
       </c>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T55" s="10" t="n">
-        <v>48.6079392947421</v>
+        <v>46.51818073624644</v>
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V55" s="10" t="n">
-        <v>48.6079392947421</v>
+        <v>46.51818073624644</v>
       </c>
       <c r="W55" s="10" t="n">
-        <v>48.6079392947421</v>
+        <v>46.51818073624644</v>
       </c>
       <c r="X55" s="10" t="n">
-        <v>24.39225381128966</v>
+        <v>24.392253811289653</v>
       </c>
       <c r="Y55" s="10" t="n">
         <v>43.80000000000001</v>
@@ -7027,22 +7027,22 @@
         <v>77.77725920308035</v>
       </c>
       <c r="AA55" s="10" t="n">
-        <v>8.049443757725586</v>
+        <v>1.2196126905644826</v>
       </c>
       <c r="AB55" s="10" t="n">
-        <v>14.892</v>
+        <v>40.296000000000014</v>
       </c>
       <c r="AC55" s="10" t="n">
-        <v>25.66649553701652</v>
+        <v>6.222180736246428</v>
       </c>
       <c r="AD55" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE55" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7076,22 +7076,22 @@
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M56" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
@@ -7115,25 +7115,25 @@
       </c>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T56" s="10" t="n">
-        <v>50.81750742047338</v>
+        <v>47.37939314232035</v>
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V56" s="10" t="n">
-        <v>50.81750742047338</v>
+        <v>47.37939314232035</v>
       </c>
       <c r="W56" s="10" t="n">
-        <v>50.81750742047338</v>
+        <v>47.37939314232035</v>
       </c>
       <c r="X56" s="10" t="n">
-        <v>28.69851729818781</v>
+        <v>28.698517298187806</v>
       </c>
       <c r="Y56" s="10" t="n">
         <v>44.60000000000001</v>
@@ -7142,22 +7142,22 @@
         <v>79.34241427900423</v>
       </c>
       <c r="AA56" s="10" t="n">
-        <v>9.470510708401976</v>
+        <v>1.4349258649093903</v>
       </c>
       <c r="AB56" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC56" s="10" t="n">
-        <v>26.18299671207139</v>
+        <v>6.347393142320339</v>
       </c>
       <c r="AD56" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE56" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7191,22 +7191,22 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
@@ -7236,22 +7236,22 @@
       </c>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T57" s="10" t="n">
-        <v>43.69539514265503</v>
+        <v>47.208386701249694</v>
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V57" s="10" t="n">
-        <v>43.69539514265503</v>
+        <v>47.208386701249694</v>
       </c>
       <c r="W57" s="10" t="n">
-        <v>43.69539514265503</v>
+        <v>47.208386701249694</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7.16</v>
@@ -7263,22 +7263,22 @@
         <v>79.50483376562131</v>
       </c>
       <c r="AA57" s="10" t="n">
-        <v>2.3628</v>
+        <v>0.358</v>
       </c>
       <c r="AB57" s="10" t="n">
-        <v>15.096</v>
+        <v>40.84799999999999</v>
       </c>
       <c r="AC57" s="10" t="n">
-        <v>26.23659514265503</v>
+        <v>6.3603867012497055</v>
       </c>
       <c r="AD57" s="8" t="inlineStr">
         <is>
-          <t>历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE57" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7312,22 +7312,22 @@
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M58" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
@@ -7351,49 +7351,49 @@
       </c>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T58" s="10" t="n">
-        <v>50.17927622916265</v>
+        <v>46.82138501536279</v>
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V58" s="10" t="n">
-        <v>50.17927622916265</v>
+        <v>46.82138501536279</v>
       </c>
       <c r="W58" s="10" t="n">
-        <v>50.17927622916265</v>
+        <v>46.82138501536279</v>
       </c>
       <c r="X58" s="10" t="n">
-        <v>27.45776679027606</v>
+        <v>27.457766790276054</v>
       </c>
       <c r="Y58" s="10" t="n">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="Z58" s="10" t="n">
         <v>79.26731269203499</v>
       </c>
       <c r="AA58" s="10" t="n">
-        <v>9.061063040791101</v>
+        <v>1.3728883395138027</v>
       </c>
       <c r="AB58" s="10" t="n">
-        <v>14.96</v>
+        <v>40.48</v>
       </c>
       <c r="AC58" s="10" t="n">
-        <v>26.15821318837155</v>
+        <v>6.3413850153628</v>
       </c>
       <c r="AD58" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE58" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7427,22 +7427,22 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
@@ -7466,25 +7466,25 @@
       </c>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T59" s="10" t="n">
-        <v>49.85700611479489</v>
+        <v>46.240713472485766</v>
       </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V59" s="10" t="n">
-        <v>49.85700611479489</v>
+        <v>46.240713472485766</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>49.85700611479489</v>
+        <v>46.240713472485766</v>
       </c>
       <c r="X59" s="10" t="n">
-        <v>27.45776679027606</v>
+        <v>27.457766790276054</v>
       </c>
       <c r="Y59" s="10" t="n">
         <v>43.4</v>
@@ -7493,22 +7493,22 @@
         <v>78.9089184060721</v>
       </c>
       <c r="AA59" s="10" t="n">
-        <v>9.061063040791101</v>
+        <v>1.3728883395138027</v>
       </c>
       <c r="AB59" s="10" t="n">
-        <v>14.756</v>
+        <v>39.928</v>
       </c>
       <c r="AC59" s="10" t="n">
-        <v>26.03994307400379</v>
+        <v>6.312713472485768</v>
       </c>
       <c r="AD59" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE59" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7546,22 +7546,22 @@
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M60" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
@@ -7585,25 +7585,25 @@
       </c>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T60" s="10" t="n">
-        <v>49.77457548806102</v>
+        <v>46.0532151387321</v>
       </c>
       <c r="U60" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V60" s="10" t="n">
-        <v>49.77457548806102</v>
+        <v>46.0532151387321</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>49.77457548806102</v>
+        <v>46.0532151387321</v>
       </c>
       <c r="X60" s="10" t="n">
-        <v>27.45776679027606</v>
+        <v>27.457766790276054</v>
       </c>
       <c r="Y60" s="10" t="n">
         <v>43.2</v>
@@ -7612,22 +7612,22 @@
         <v>78.86518923415126</v>
       </c>
       <c r="AA60" s="10" t="n">
-        <v>9.061063040791101</v>
+        <v>1.3728883395138027</v>
       </c>
       <c r="AB60" s="10" t="n">
-        <v>14.688</v>
+        <v>39.744</v>
       </c>
       <c r="AC60" s="10" t="n">
-        <v>26.02551244726992</v>
+        <v>6.3092151387321005</v>
       </c>
       <c r="AD60" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE60" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7665,22 +7665,22 @@
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
@@ -7704,22 +7704,22 @@
       </c>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T61" s="10" t="n">
-        <v>49.4543148815154</v>
+        <v>45.64672243346007</v>
       </c>
       <c r="U61" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V61" s="10" t="n">
-        <v>49.4543148815154</v>
+        <v>45.64672243346007</v>
       </c>
       <c r="W61" s="10" t="n">
-        <v>49.4543148815154</v>
+        <v>45.64672243346007</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>27.38056013179571</v>
@@ -7731,22 +7731,22 @@
         <v>78.38403041825094</v>
       </c>
       <c r="AA61" s="10" t="n">
-        <v>9.035584843492586</v>
+        <v>1.3690280065897855</v>
       </c>
       <c r="AB61" s="10" t="n">
-        <v>14.552</v>
+        <v>39.376</v>
       </c>
       <c r="AC61" s="10" t="n">
-        <v>25.86673003802281</v>
+        <v>6.270722433460076</v>
       </c>
       <c r="AD61" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE61" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7784,22 +7784,22 @@
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M62" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
@@ -7823,22 +7823,22 @@
       </c>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T62" s="10" t="n">
-        <v>50.03487539285126</v>
+        <v>45.64345056119722</v>
       </c>
       <c r="U62" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V62" s="10" t="n">
-        <v>50.03487539285126</v>
+        <v>45.64345056119722</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>50.03487539285126</v>
+        <v>45.64345056119722</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>29.18073281185673</v>
@@ -7850,22 +7850,22 @@
         <v>78.34313201496526</v>
       </c>
       <c r="AA62" s="10" t="n">
-        <v>9.629641827912721</v>
+        <v>1.4590366405928363</v>
       </c>
       <c r="AB62" s="10" t="n">
-        <v>14.552</v>
+        <v>39.376</v>
       </c>
       <c r="AC62" s="10" t="n">
-        <v>25.85323356493854</v>
+        <v>6.267450561197221</v>
       </c>
       <c r="AD62" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE62" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -7903,22 +7903,22 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
@@ -7942,25 +7942,25 @@
       </c>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T63" s="10" t="n">
-        <v>49.37501742941038</v>
+        <v>44.64925949743956</v>
       </c>
       <c r="U63" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V63" s="10" t="n">
-        <v>49.37501742941038</v>
+        <v>44.64925949743956</v>
       </c>
       <c r="W63" s="10" t="n">
-        <v>49.37501742941038</v>
+        <v>44.64925949743956</v>
       </c>
       <c r="X63" s="10" t="n">
-        <v>29.13885455294603</v>
+        <v>29.138854552946025</v>
       </c>
       <c r="Y63" s="10" t="n">
         <v>41.8</v>
@@ -7969,22 +7969,22 @@
         <v>77.41574371799452</v>
       </c>
       <c r="AA63" s="10" t="n">
-        <v>9.615822002472187</v>
+        <v>1.4569427276473013</v>
       </c>
       <c r="AB63" s="10" t="n">
-        <v>14.212</v>
+        <v>38.455999999999996</v>
       </c>
       <c r="AC63" s="10" t="n">
-        <v>25.54719542693819</v>
+        <v>6.193259497439561</v>
       </c>
       <c r="AD63" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE63" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8022,22 +8022,22 @@
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M64" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
@@ -8061,25 +8061,25 @@
       </c>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T64" s="10" t="n">
-        <v>49.62787195786916</v>
+        <v>45.04558786797502</v>
       </c>
       <c r="U64" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V64" s="10" t="n">
-        <v>49.62787195786916</v>
+        <v>45.04558786797502</v>
       </c>
       <c r="W64" s="10" t="n">
-        <v>49.62787195786916</v>
+        <v>45.04558786797502</v>
       </c>
       <c r="X64" s="10" t="n">
-        <v>29.13885455294603</v>
+        <v>29.138854552946025</v>
       </c>
       <c r="Y64" s="10" t="n">
         <v>42.2</v>
@@ -8088,22 +8088,22 @@
         <v>77.76984834968779</v>
       </c>
       <c r="AA64" s="10" t="n">
-        <v>9.615822002472187</v>
+        <v>1.4569427276473013</v>
       </c>
       <c r="AB64" s="10" t="n">
-        <v>14.348</v>
+        <v>38.824</v>
       </c>
       <c r="AC64" s="10" t="n">
-        <v>25.66404995539697</v>
+        <v>6.221587867975023</v>
       </c>
       <c r="AD64" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE64" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8141,22 +8141,22 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
@@ -8180,25 +8180,25 @@
       </c>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T65" s="10" t="n">
-        <v>48.91040077507856</v>
+        <v>44.40339101083674</v>
       </c>
       <c r="U65" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V65" s="10" t="n">
-        <v>48.91040077507856</v>
+        <v>44.40339101083674</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>48.91040077507856</v>
+        <v>44.40339101083674</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>28.71034198599094</v>
+        <v>28.710341985990937</v>
       </c>
       <c r="Y65" s="10" t="n">
         <v>41.6</v>
@@ -8207,22 +8207,22 @@
         <v>76.64238763545923</v>
       </c>
       <c r="AA65" s="10" t="n">
-        <v>9.474412855377009</v>
+        <v>1.4355170992995467</v>
       </c>
       <c r="AB65" s="10" t="n">
-        <v>14.144</v>
+        <v>38.272000000000006</v>
       </c>
       <c r="AC65" s="10" t="n">
-        <v>25.29198791970155</v>
+        <v>6.131391010836738</v>
       </c>
       <c r="AD65" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE65" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8260,22 +8260,22 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M66" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
@@ -8299,49 +8299,49 @@
       </c>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T66" s="10" t="n">
-        <v>49.02785910861005</v>
+        <v>44.1545881798917</v>
       </c>
       <c r="U66" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V66" s="10" t="n">
-        <v>49.02785910861005</v>
+        <v>44.1545881798917</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>49.02785910861005</v>
+        <v>44.1545881798917</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>30.08237232289951</v>
+        <v>30.082372322899506</v>
       </c>
       <c r="Y66" s="10" t="n">
-        <v>41.40000000000001</v>
+        <v>41.400000000000006</v>
       </c>
       <c r="Z66" s="10" t="n">
         <v>75.8323522486461</v>
       </c>
       <c r="AA66" s="10" t="n">
-        <v>9.927182866556837</v>
+        <v>1.5041186161449753</v>
       </c>
       <c r="AB66" s="10" t="n">
-        <v>14.076</v>
+        <v>38.08800000000001</v>
       </c>
       <c r="AC66" s="10" t="n">
-        <v>25.02467624205321</v>
+        <v>6.0665881798916885</v>
       </c>
       <c r="AD66" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE66" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8379,22 +8379,22 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
@@ -8418,22 +8418,22 @@
       </c>
       <c r="S67" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T67" s="10" t="n">
-        <v>48.9615291705645</v>
+        <v>43.96934898814088</v>
       </c>
       <c r="U67" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V67" s="10" t="n">
-        <v>48.9615291705645</v>
+        <v>43.96934898814088</v>
       </c>
       <c r="W67" s="10" t="n">
-        <v>48.9615291705645</v>
+        <v>43.96934898814088</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>30.10292301358584</v>
@@ -8445,22 +8445,22 @@
         <v>75.81686235176115</v>
       </c>
       <c r="AA67" s="10" t="n">
-        <v>9.933964594483326</v>
+        <v>1.505146150679292</v>
       </c>
       <c r="AB67" s="10" t="n">
-        <v>14.008</v>
+        <v>37.90399999999999</v>
       </c>
       <c r="AC67" s="10" t="n">
-        <v>25.01956457608118</v>
+        <v>6.065348988140892</v>
       </c>
       <c r="AD67" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE67" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8498,22 +8498,22 @@
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M68" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
@@ -8537,49 +8537,49 @@
       </c>
       <c r="S68" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T68" s="10" t="n">
-        <v>49.21775431331479</v>
+        <v>44.20226879109164</v>
       </c>
       <c r="U68" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V68" s="10" t="n">
-        <v>49.21775431331479</v>
+        <v>44.20226879109164</v>
       </c>
       <c r="W68" s="10" t="n">
-        <v>49.21775431331479</v>
+        <v>44.20226879109164</v>
       </c>
       <c r="X68" s="10" t="n">
-        <v>30.06180469715699</v>
+        <v>30.061804697156987</v>
       </c>
       <c r="Y68" s="10" t="n">
-        <v>41.40000000000001</v>
+        <v>41.400000000000006</v>
       </c>
       <c r="Z68" s="10" t="n">
         <v>76.4283598886454</v>
       </c>
       <c r="AA68" s="10" t="n">
-        <v>9.920395550061805</v>
+        <v>1.5030902348578494</v>
       </c>
       <c r="AB68" s="10" t="n">
-        <v>14.076</v>
+        <v>38.08800000000001</v>
       </c>
       <c r="AC68" s="10" t="n">
-        <v>25.22135876325298</v>
+        <v>6.114268791091632</v>
       </c>
       <c r="AD68" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE68" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8617,22 +8617,22 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
@@ -8656,49 +8656,49 @@
       </c>
       <c r="S69" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T69" s="10" t="n">
-        <v>49.31037915467152</v>
+        <v>44.22472329808721</v>
       </c>
       <c r="U69" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V69" s="10" t="n">
-        <v>49.31037915467152</v>
+        <v>44.22472329808721</v>
       </c>
       <c r="W69" s="10" t="n">
-        <v>49.31037915467152</v>
+        <v>44.22472329808721</v>
       </c>
       <c r="X69" s="10" t="n">
-        <v>30.06180469715699</v>
+        <v>30.061804697156987</v>
       </c>
       <c r="Y69" s="10" t="n">
-        <v>41.40000000000001</v>
+        <v>41.400000000000006</v>
       </c>
       <c r="Z69" s="10" t="n">
         <v>76.70904122609005</v>
       </c>
       <c r="AA69" s="10" t="n">
-        <v>9.920395550061805</v>
+        <v>1.5030902348578494</v>
       </c>
       <c r="AB69" s="10" t="n">
-        <v>14.076</v>
+        <v>38.08800000000001</v>
       </c>
       <c r="AC69" s="10" t="n">
-        <v>25.31398360460972</v>
+        <v>6.136723298087204</v>
       </c>
       <c r="AD69" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE69" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8736,22 +8736,22 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M70" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
@@ -8775,49 +8775,49 @@
       </c>
       <c r="S70" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T70" s="10" t="n">
-        <v>49.65838183756387</v>
+        <v>45.43020651206927</v>
       </c>
       <c r="U70" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V70" s="10" t="n">
-        <v>49.65838183756387</v>
+        <v>45.43020651206927</v>
       </c>
       <c r="W70" s="10" t="n">
-        <v>49.65838183756387</v>
+        <v>45.43020651206927</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>28.61145447053977</v>
+        <v>28.611454470539755</v>
       </c>
       <c r="Y70" s="10" t="n">
-        <v>42.59999999999999</v>
+        <v>42.599999999999994</v>
       </c>
       <c r="Z70" s="10" t="n">
         <v>77.97758140086592</v>
       </c>
       <c r="AA70" s="10" t="n">
-        <v>9.441779975278124</v>
+        <v>1.4305727235269876</v>
       </c>
       <c r="AB70" s="10" t="n">
-        <v>14.484</v>
+        <v>39.19199999999999</v>
       </c>
       <c r="AC70" s="10" t="n">
-        <v>25.73260186228575</v>
+        <v>6.238206512069273</v>
       </c>
       <c r="AD70" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE70" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8855,22 +8855,22 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
@@ -8894,49 +8894,49 @@
       </c>
       <c r="S71" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T71" s="10" t="n">
-        <v>50.02583719604181</v>
+        <v>45.459603286105484</v>
       </c>
       <c r="U71" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V71" s="10" t="n">
-        <v>50.02583719604181</v>
+        <v>45.459603286105484</v>
       </c>
       <c r="W71" s="10" t="n">
-        <v>50.02583719604181</v>
+        <v>45.459603286105484</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>29.35749588138385</v>
+        <v>29.35749588138386</v>
       </c>
       <c r="Y71" s="10" t="n">
-        <v>42.59999999999999</v>
+        <v>42.599999999999994</v>
       </c>
       <c r="Z71" s="10" t="n">
         <v>78.34504107631861</v>
       </c>
       <c r="AA71" s="10" t="n">
-        <v>9.687973640856672</v>
+        <v>1.467874794069193</v>
       </c>
       <c r="AB71" s="10" t="n">
-        <v>14.484</v>
+        <v>39.19199999999999</v>
       </c>
       <c r="AC71" s="10" t="n">
-        <v>25.85386355518514</v>
+        <v>6.267603286105489</v>
       </c>
       <c r="AD71" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE71" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -8974,22 +8974,22 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M72" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
@@ -9013,49 +9013,49 @@
       </c>
       <c r="S72" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T72" s="10" t="n">
-        <v>50.03760682595423</v>
+        <v>45.2537510116639</v>
       </c>
       <c r="U72" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V72" s="10" t="n">
-        <v>50.03760682595423</v>
+        <v>45.2537510116639</v>
       </c>
       <c r="W72" s="10" t="n">
-        <v>50.03760682595423</v>
+        <v>45.2537510116639</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>29.87237546315356</v>
       </c>
       <c r="Y72" s="10" t="n">
-        <v>42.40000000000001</v>
+        <v>42.400000000000006</v>
       </c>
       <c r="Z72" s="10" t="n">
         <v>78.07188764579863</v>
       </c>
       <c r="AA72" s="10" t="n">
-        <v>9.857883902840674</v>
+        <v>1.493618773157678</v>
       </c>
       <c r="AB72" s="10" t="n">
-        <v>14.416</v>
+        <v>39.00800000000001</v>
       </c>
       <c r="AC72" s="10" t="n">
-        <v>25.76372292311355</v>
+        <v>6.24575101166389</v>
       </c>
       <c r="AD72" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE72" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9093,22 +9093,22 @@
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
@@ -9132,25 +9132,25 @@
       </c>
       <c r="S73" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T73" s="10" t="n">
-        <v>50.76843885205594</v>
+        <v>46.27180283367067</v>
       </c>
       <c r="U73" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V73" s="10" t="n">
-        <v>50.76843885205594</v>
+        <v>46.27180283367067</v>
       </c>
       <c r="W73" s="10" t="n">
-        <v>50.76843885205594</v>
+        <v>46.27180283367067</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>29.83106716110424</v>
+        <v>29.831067161104237</v>
       </c>
       <c r="Y73" s="10" t="n">
         <v>43.4</v>
@@ -9159,22 +9159,22 @@
         <v>79.29753542088343</v>
       </c>
       <c r="AA73" s="10" t="n">
-        <v>9.8442521631644</v>
+        <v>1.4915533580552118</v>
       </c>
       <c r="AB73" s="10" t="n">
-        <v>14.756</v>
+        <v>39.928</v>
       </c>
       <c r="AC73" s="10" t="n">
-        <v>26.16818668889153</v>
+        <v>6.343802833670675</v>
       </c>
       <c r="AD73" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE73" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9212,22 +9212,22 @@
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M74" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
@@ -9251,25 +9251,25 @@
       </c>
       <c r="S74" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T74" s="10" t="n">
-        <v>49.96507838555767</v>
+        <v>45.04558786797502</v>
       </c>
       <c r="U74" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V74" s="10" t="n">
-        <v>49.96507838555767</v>
+        <v>45.04558786797502</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>49.96507838555767</v>
+        <v>45.04558786797502</v>
       </c>
       <c r="X74" s="10" t="n">
-        <v>30.16069221260816</v>
+        <v>30.160692212608158</v>
       </c>
       <c r="Y74" s="10" t="n">
         <v>42.2</v>
@@ -9278,22 +9278,22 @@
         <v>77.76984834968779</v>
       </c>
       <c r="AA74" s="10" t="n">
-        <v>9.953028430160693</v>
+        <v>1.508034610630408</v>
       </c>
       <c r="AB74" s="10" t="n">
-        <v>14.348</v>
+        <v>38.824</v>
       </c>
       <c r="AC74" s="10" t="n">
-        <v>25.66404995539697</v>
+        <v>6.221587867975023</v>
       </c>
       <c r="AD74" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE74" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9331,22 +9331,22 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
@@ -9370,49 +9370,49 @@
       </c>
       <c r="S75" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T75" s="10" t="n">
-        <v>49.37717305432815</v>
+        <v>44.23300475737394</v>
       </c>
       <c r="U75" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V75" s="10" t="n">
-        <v>49.37717305432815</v>
+        <v>44.23300475737394</v>
       </c>
       <c r="W75" s="10" t="n">
-        <v>49.37717305432815</v>
+        <v>44.23300475737394</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>30.16069221260816</v>
+        <v>30.160692212608158</v>
       </c>
       <c r="Y75" s="10" t="n">
-        <v>41.40000000000001</v>
+        <v>41.400000000000006</v>
       </c>
       <c r="Z75" s="10" t="n">
         <v>76.81255946717413</v>
       </c>
       <c r="AA75" s="10" t="n">
-        <v>9.953028430160693</v>
+        <v>1.508034610630408</v>
       </c>
       <c r="AB75" s="10" t="n">
-        <v>14.076</v>
+        <v>38.08800000000001</v>
       </c>
       <c r="AC75" s="10" t="n">
-        <v>25.34814462416746</v>
+        <v>6.14500475737393</v>
       </c>
       <c r="AD75" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE75" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9450,22 +9450,22 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M76" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
@@ -9489,25 +9489,25 @@
       </c>
       <c r="S76" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T76" s="10" t="n">
-        <v>49.9903193586287</v>
+        <v>44.85091861641959</v>
       </c>
       <c r="U76" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V76" s="10" t="n">
-        <v>49.9903193586287</v>
+        <v>44.85091861641959</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>49.9903193586287</v>
+        <v>44.85091861641959</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>30.57660626029654</v>
+        <v>30.576606260296547</v>
       </c>
       <c r="Y76" s="10" t="n">
         <v>41.99999999999999</v>
@@ -9516,22 +9516,22 @@
         <v>77.63648270524497</v>
       </c>
       <c r="AA76" s="10" t="n">
-        <v>10.09028006589786</v>
+        <v>1.5288303130148273</v>
       </c>
       <c r="AB76" s="10" t="n">
-        <v>14.28</v>
+        <v>38.63999999999999</v>
       </c>
       <c r="AC76" s="10" t="n">
-        <v>25.62003929273084</v>
+        <v>6.2109186164195975</v>
       </c>
       <c r="AD76" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE76" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9569,22 +9569,22 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
@@ -9608,49 +9608,49 @@
       </c>
       <c r="S77" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T77" s="10" t="n">
-        <v>50.95752426134457</v>
+        <v>46.43241686404547</v>
       </c>
       <c r="U77" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V77" s="10" t="n">
-        <v>50.95752426134457</v>
+        <v>46.43241686404547</v>
       </c>
       <c r="W77" s="10" t="n">
-        <v>50.95752426134457</v>
+        <v>46.43241686404547</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>30.49031726411208</v>
+        <v>30.490317264112083</v>
       </c>
       <c r="Y77" s="10" t="n">
-        <v>43.59999999999999</v>
+        <v>43.599999999999994</v>
       </c>
       <c r="Z77" s="10" t="n">
         <v>79.00521080056845</v>
       </c>
       <c r="AA77" s="10" t="n">
-        <v>10.06180469715699</v>
+        <v>1.5245158632056042</v>
       </c>
       <c r="AB77" s="10" t="n">
-        <v>14.824</v>
+        <v>40.111999999999995</v>
       </c>
       <c r="AC77" s="10" t="n">
-        <v>26.07171956418759</v>
+        <v>6.320416864045476</v>
       </c>
       <c r="AD77" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE77" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9688,22 +9688,22 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M78" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N78" s="8" t="inlineStr">
@@ -9727,49 +9727,49 @@
       </c>
       <c r="S78" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T78" s="10" t="n">
-        <v>51.2578547052839</v>
+        <v>46.84916691372665</v>
       </c>
       <c r="U78" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V78" s="10" t="n">
-        <v>51.2578547052839</v>
+        <v>46.84916691372665</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>51.2578547052839</v>
+        <v>46.84916691372665</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>30.37891268533772</v>
+        <v>30.37891268533773</v>
       </c>
       <c r="Y78" s="10" t="n">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="Z78" s="10" t="n">
         <v>79.61458642158317</v>
       </c>
       <c r="AA78" s="10" t="n">
-        <v>10.02504118616145</v>
+        <v>1.5189456342668866</v>
       </c>
       <c r="AB78" s="10" t="n">
-        <v>14.96</v>
+        <v>40.48</v>
       </c>
       <c r="AC78" s="10" t="n">
-        <v>26.27281351912245</v>
+        <v>6.369166913726653</v>
       </c>
       <c r="AD78" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE78" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9807,22 +9807,22 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
@@ -9846,25 +9846,25 @@
       </c>
       <c r="S79" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T79" s="10" t="n">
-        <v>51.69942580148197</v>
+        <v>47.25008802942222</v>
       </c>
       <c r="U79" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V79" s="10" t="n">
-        <v>51.69942580148197</v>
+        <v>47.25008802942222</v>
       </c>
       <c r="W79" s="10" t="n">
-        <v>51.69942580148197</v>
+        <v>47.25008802942222</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>30.89337175792507</v>
+        <v>30.893371757925067</v>
       </c>
       <c r="Y79" s="10" t="n">
         <v>44.39999999999999</v>
@@ -9873,22 +9873,22 @@
         <v>80.0261003677779</v>
       </c>
       <c r="AA79" s="10" t="n">
-        <v>10.19481268011527</v>
+        <v>1.5446685878962534</v>
       </c>
       <c r="AB79" s="10" t="n">
-        <v>15.096</v>
+        <v>40.84799999999999</v>
       </c>
       <c r="AC79" s="10" t="n">
-        <v>26.40861312136671</v>
+        <v>6.402088029422232</v>
       </c>
       <c r="AD79" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE79" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -9926,22 +9926,22 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M80" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
@@ -9965,49 +9965,49 @@
       </c>
       <c r="S80" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T80" s="10" t="n">
-        <v>51.77080506830319</v>
+        <v>47.81309453208397</v>
       </c>
       <c r="U80" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V80" s="10" t="n">
-        <v>51.77080506830319</v>
+        <v>47.81309453208397</v>
       </c>
       <c r="W80" s="10" t="n">
-        <v>51.77080506830319</v>
+        <v>47.81309453208397</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>30.35390946502058</v>
       </c>
       <c r="Y80" s="10" t="n">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="Z80" s="10" t="n">
         <v>80.1636816510497</v>
       </c>
       <c r="AA80" s="10" t="n">
-        <v>10.01679012345679</v>
+        <v>1.517695473251029</v>
       </c>
       <c r="AB80" s="10" t="n">
-        <v>15.3</v>
+        <v>41.4</v>
       </c>
       <c r="AC80" s="10" t="n">
-        <v>26.4540149448464</v>
+        <v>6.413094532083976</v>
       </c>
       <c r="AD80" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE80" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10045,22 +10045,22 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
@@ -10084,49 +10084,49 @@
       </c>
       <c r="S81" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T81" s="10" t="n">
-        <v>52.00817195646209</v>
+        <v>48.00492746730083</v>
       </c>
       <c r="U81" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V81" s="10" t="n">
-        <v>52.00817195646209</v>
+        <v>48.00492746730083</v>
       </c>
       <c r="W81" s="10" t="n">
-        <v>52.00817195646209</v>
+        <v>48.00492746730083</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>30.76923076923077</v>
+        <v>30.769230769230774</v>
       </c>
       <c r="Y81" s="10" t="n">
-        <v>45.2</v>
+        <v>45.199999999999996</v>
       </c>
       <c r="Z81" s="10" t="n">
         <v>80.26159334126041</v>
       </c>
       <c r="AA81" s="10" t="n">
-        <v>10.15384615384616</v>
+        <v>1.5384615384615388</v>
       </c>
       <c r="AB81" s="10" t="n">
-        <v>15.368</v>
+        <v>41.583999999999996</v>
       </c>
       <c r="AC81" s="10" t="n">
-        <v>26.48632580261593</v>
+        <v>6.4209274673008325</v>
       </c>
       <c r="AD81" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE81" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10164,22 +10164,22 @@
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M82" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
@@ -10203,49 +10203,49 @@
       </c>
       <c r="S82" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T82" s="10" t="n">
-        <v>52.00817195646209</v>
+        <v>48.00492746730083</v>
       </c>
       <c r="U82" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V82" s="10" t="n">
-        <v>52.00817195646209</v>
+        <v>48.00492746730083</v>
       </c>
       <c r="W82" s="10" t="n">
-        <v>52.00817195646209</v>
+        <v>48.00492746730083</v>
       </c>
       <c r="X82" s="10" t="n">
-        <v>30.76923076923077</v>
+        <v>30.769230769230774</v>
       </c>
       <c r="Y82" s="10" t="n">
-        <v>45.2</v>
+        <v>45.199999999999996</v>
       </c>
       <c r="Z82" s="10" t="n">
         <v>80.26159334126041</v>
       </c>
       <c r="AA82" s="10" t="n">
-        <v>10.15384615384616</v>
+        <v>1.5384615384615388</v>
       </c>
       <c r="AB82" s="10" t="n">
-        <v>15.368</v>
+        <v>41.583999999999996</v>
       </c>
       <c r="AC82" s="10" t="n">
-        <v>26.48632580261593</v>
+        <v>6.4209274673008325</v>
       </c>
       <c r="AD82" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE82" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10283,22 +10283,22 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
@@ -10322,25 +10322,25 @@
       </c>
       <c r="S83" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T83" s="10" t="n">
-        <v>51.45322793817775</v>
+        <v>47.06504581377384</v>
       </c>
       <c r="U83" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V83" s="10" t="n">
-        <v>51.45322793817775</v>
+        <v>47.06504581377384</v>
       </c>
       <c r="W83" s="10" t="n">
-        <v>51.45322793817775</v>
+        <v>47.06504581377384</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>30.36640592836558</v>
+        <v>30.366405928365584</v>
       </c>
       <c r="Y83" s="10" t="n">
         <v>44.2</v>
@@ -10349,22 +10349,22 @@
         <v>80.01307267217304</v>
       </c>
       <c r="AA83" s="10" t="n">
-        <v>10.02091395636064</v>
+        <v>1.5183202964182791</v>
       </c>
       <c r="AB83" s="10" t="n">
-        <v>15.028</v>
+        <v>40.664</v>
       </c>
       <c r="AC83" s="10" t="n">
-        <v>26.4043139818171</v>
+        <v>6.401045813773843</v>
       </c>
       <c r="AD83" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE83" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10402,22 +10402,22 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M84" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
@@ -10441,25 +10441,25 @@
       </c>
       <c r="S84" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T84" s="10" t="n">
-        <v>51.45730560415349</v>
+        <v>47.06866916800667</v>
       </c>
       <c r="U84" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V84" s="10" t="n">
-        <v>51.45730560415349</v>
+        <v>47.06866916800667</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>51.45730560415349</v>
+        <v>47.06866916800667</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>30.33347056401811</v>
+        <v>30.333470564018114</v>
       </c>
       <c r="Y84" s="10" t="n">
         <v>44.2</v>
@@ -10468,22 +10468,22 @@
         <v>80.05836460008338</v>
       </c>
       <c r="AA84" s="10" t="n">
-        <v>10.01004528612598</v>
+        <v>1.5166735282009056</v>
       </c>
       <c r="AB84" s="10" t="n">
-        <v>15.028</v>
+        <v>40.664</v>
       </c>
       <c r="AC84" s="10" t="n">
-        <v>26.41926031802751</v>
+        <v>6.40466916800667</v>
       </c>
       <c r="AD84" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE84" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10521,22 +10521,22 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N85" s="8" t="inlineStr">
@@ -10560,49 +10560,49 @@
       </c>
       <c r="S85" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T85" s="10" t="n">
-        <v>51.69125872453652</v>
+        <v>47.630565359671564</v>
       </c>
       <c r="U85" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V85" s="10" t="n">
-        <v>51.69125872453652</v>
+        <v>47.630565359671564</v>
       </c>
       <c r="W85" s="10" t="n">
-        <v>51.69125872453652</v>
+        <v>47.630565359671564</v>
       </c>
       <c r="X85" s="10" t="n">
-        <v>30.30053519967065</v>
+        <v>30.300535199670648</v>
       </c>
       <c r="Y85" s="10" t="n">
-        <v>44.8</v>
+        <v>44.800000000000004</v>
       </c>
       <c r="Z85" s="10" t="n">
         <v>80.18206699589457</v>
       </c>
       <c r="AA85" s="10" t="n">
-        <v>9.999176615891313</v>
+        <v>1.5150267599835325</v>
       </c>
       <c r="AB85" s="10" t="n">
-        <v>15.232</v>
+        <v>41.216</v>
       </c>
       <c r="AC85" s="10" t="n">
-        <v>26.46008210864521</v>
+        <v>6.414565359671566</v>
       </c>
       <c r="AD85" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE85" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10640,22 +10640,22 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M86" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N86" s="8" t="inlineStr">
@@ -10679,49 +10679,49 @@
       </c>
       <c r="S86" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T86" s="10" t="n">
-        <v>52.11343329070099</v>
+        <v>47.82504480822082</v>
       </c>
       <c r="U86" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V86" s="10" t="n">
-        <v>52.11343329070099</v>
+        <v>47.82504480822082</v>
       </c>
       <c r="W86" s="10" t="n">
-        <v>52.11343329070099</v>
+        <v>47.82504480822082</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>31.24279835390947</v>
+        <v>31.242798353909464</v>
       </c>
       <c r="Y86" s="10" t="n">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="Z86" s="10" t="n">
         <v>80.31306010276019</v>
       </c>
       <c r="AA86" s="10" t="n">
-        <v>10.31012345679012</v>
+        <v>1.5621399176954731</v>
       </c>
       <c r="AB86" s="10" t="n">
-        <v>15.3</v>
+        <v>41.4</v>
       </c>
       <c r="AC86" s="10" t="n">
-        <v>26.50330983391086</v>
+        <v>6.425044808220815</v>
       </c>
       <c r="AD86" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE86" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10759,22 +10759,22 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N87" s="8" t="inlineStr">
@@ -10798,25 +10798,25 @@
       </c>
       <c r="S87" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T87" s="10" t="n">
-        <v>52.30123201128779</v>
+        <v>48.19563549731983</v>
       </c>
       <c r="U87" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V87" s="10" t="n">
-        <v>52.30123201128779</v>
+        <v>48.19563549731983</v>
       </c>
       <c r="W87" s="10" t="n">
-        <v>52.30123201128779</v>
+        <v>48.19563549731983</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>31.3673805601318</v>
+        <v>31.36738056013179</v>
       </c>
       <c r="Y87" s="10" t="n">
         <v>45.39999999999999</v>
@@ -10825,22 +10825,22 @@
         <v>80.34544371649791</v>
       </c>
       <c r="AA87" s="10" t="n">
-        <v>10.35123558484349</v>
+        <v>1.5683690280065894</v>
       </c>
       <c r="AB87" s="10" t="n">
-        <v>15.436</v>
+        <v>41.767999999999994</v>
       </c>
       <c r="AC87" s="10" t="n">
-        <v>26.51399642644431</v>
+        <v>6.427635497319833</v>
       </c>
       <c r="AD87" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE87" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10878,22 +10878,22 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M88" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">B · 观察区间</t>
         </is>
       </c>
       <c r="N88" s="8" t="inlineStr">
@@ -10917,25 +10917,25 @@
       </c>
       <c r="S88" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T88" s="10" t="n">
-        <v>52.43339995197007</v>
+        <v>48.39519136172766</v>
       </c>
       <c r="U88" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="V88" s="10" t="n">
-        <v>52.43339995197007</v>
+        <v>48.39519136172766</v>
       </c>
       <c r="W88" s="10" t="n">
-        <v>52.43339995197007</v>
+        <v>48.39519136172766</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>31.3673805601318</v>
+        <v>31.36738056013179</v>
       </c>
       <c r="Y88" s="10" t="n">
         <v>45.60000000000001</v>
@@ -10944,22 +10944,22 @@
         <v>80.53989202159568</v>
       </c>
       <c r="AA88" s="10" t="n">
-        <v>10.35123558484349</v>
+        <v>1.5683690280065894</v>
       </c>
       <c r="AB88" s="10" t="n">
-        <v>15.504</v>
+        <v>41.952000000000005</v>
       </c>
       <c r="AC88" s="10" t="n">
-        <v>26.57816436712658</v>
+        <v>6.443191361727654</v>
       </c>
       <c r="AD88" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE88" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N89" s="8" t="inlineStr">
@@ -11036,25 +11036,25 @@
       </c>
       <c r="S89" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T89" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="U89" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V89" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="W89" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>28.74074074074075</v>
+        <v>28.740740740740748</v>
       </c>
       <c r="Y89" s="10" t="n">
         <v>43.00000000000001</v>
@@ -11063,22 +11063,22 @@
         <v>78.43453510436434</v>
       </c>
       <c r="AA89" s="10" t="n">
-        <v>9.484444444444447</v>
+        <v>1.4370370370370376</v>
       </c>
       <c r="AB89" s="10" t="n">
-        <v>14.62</v>
+        <v>39.56</v>
       </c>
       <c r="AC89" s="10" t="n">
-        <v>25.88339658444023</v>
+        <v>6.274762808349148</v>
       </c>
       <c r="AD89" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE89" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11116,22 +11116,22 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M90" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N90" s="8" t="inlineStr">
@@ -11155,25 +11155,25 @@
       </c>
       <c r="S90" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T90" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U90" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V90" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W90" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y90" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11182,22 +11182,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA90" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB90" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC90" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD90" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE90" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11235,22 +11235,22 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N91" s="8" t="inlineStr">
@@ -11274,25 +11274,25 @@
       </c>
       <c r="S91" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T91" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U91" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V91" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W91" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y91" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11301,22 +11301,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA91" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB91" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC91" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD91" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE91" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11354,22 +11354,22 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M92" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N92" s="8" t="inlineStr">
@@ -11393,25 +11393,25 @@
       </c>
       <c r="S92" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T92" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U92" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V92" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W92" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y92" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11420,22 +11420,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA92" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB92" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC92" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD92" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE92" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11473,22 +11473,22 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N93" s="8" t="inlineStr">
@@ -11512,25 +11512,25 @@
       </c>
       <c r="S93" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T93" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U93" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V93" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y93" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11539,22 +11539,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA93" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB93" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC93" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD93" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE93" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11592,22 +11592,22 @@
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M94" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N94" s="8" t="inlineStr">
@@ -11631,25 +11631,25 @@
       </c>
       <c r="S94" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T94" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U94" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V94" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W94" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y94" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11658,22 +11658,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA94" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB94" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC94" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD94" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE94" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11711,22 +11711,22 @@
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N95" s="8" t="inlineStr">
@@ -11750,25 +11750,25 @@
       </c>
       <c r="S95" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T95" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U95" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V95" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W95" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y95" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11777,22 +11777,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA95" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB95" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC95" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD95" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE95" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11830,22 +11830,22 @@
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>A · 重点配置区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M96" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N96" s="8" t="inlineStr">
@@ -11869,25 +11869,25 @@
       </c>
       <c r="S96" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T96" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="U96" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V96" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>52.09503614020787</v>
+        <v>47.44132112709548</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>31.79571663920922</v>
+        <v>31.795716639209225</v>
       </c>
       <c r="Y96" s="10" t="n">
         <v>44.60000000000001</v>
@@ -11896,22 +11896,22 @@
         <v>80.11651408869338</v>
       </c>
       <c r="AA96" s="10" t="n">
-        <v>10.49258649093905</v>
+        <v>1.5897858319604612</v>
       </c>
       <c r="AB96" s="10" t="n">
-        <v>15.164</v>
+        <v>41.03200000000001</v>
       </c>
       <c r="AC96" s="10" t="n">
-        <v>26.43844964926882</v>
+        <v>6.40932112709547</v>
       </c>
       <c r="AD96" s="8" t="inlineStr">
         <is>
-          <t>参考评分；日期未对齐；历史数据试算</t>
+          <t xml:space="preserve">日期未对齐；历史数据试算</t>
         </is>
       </c>
       <c r="AE96" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -11949,22 +11949,22 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N97" s="8" t="inlineStr">
@@ -11988,25 +11988,25 @@
       </c>
       <c r="S97" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T97" s="10" t="n">
-        <v>51.25885118139834</v>
+        <v>46.630197289780476</v>
       </c>
       <c r="U97" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V97" s="10" t="n">
-        <v>51.25885118139834</v>
+        <v>46.630197289780476</v>
       </c>
       <c r="W97" s="10" t="n">
-        <v>51.25885118139834</v>
+        <v>46.630197289780476</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>31.02511321531495</v>
+        <v>31.025113215314946</v>
       </c>
       <c r="Y97" s="10" t="n">
         <v>43.80000000000001</v>
@@ -12015,22 +12015,22 @@
         <v>79.17746612225577</v>
       </c>
       <c r="AA97" s="10" t="n">
-        <v>10.23828736105393</v>
+        <v>1.5512556607657473</v>
       </c>
       <c r="AB97" s="10" t="n">
-        <v>14.892</v>
+        <v>40.296000000000014</v>
       </c>
       <c r="AC97" s="10" t="n">
-        <v>26.1285638203444</v>
+        <v>6.3341972897804615</v>
       </c>
       <c r="AD97" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE97" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12068,22 +12068,22 @@
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M98" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N98" s="8" t="inlineStr">
@@ -12107,25 +12107,25 @@
       </c>
       <c r="S98" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T98" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="U98" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V98" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>28.74074074074075</v>
+        <v>28.740740740740748</v>
       </c>
       <c r="Y98" s="10" t="n">
         <v>43.00000000000001</v>
@@ -12134,22 +12134,22 @@
         <v>78.43453510436434</v>
       </c>
       <c r="AA98" s="10" t="n">
-        <v>9.484444444444447</v>
+        <v>1.4370370370370376</v>
       </c>
       <c r="AB98" s="10" t="n">
-        <v>14.62</v>
+        <v>39.56</v>
       </c>
       <c r="AC98" s="10" t="n">
-        <v>25.88339658444023</v>
+        <v>6.274762808349148</v>
       </c>
       <c r="AD98" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE98" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12187,22 +12187,22 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N99" s="8" t="inlineStr">
@@ -12226,25 +12226,25 @@
       </c>
       <c r="S99" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T99" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="U99" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V99" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="W99" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>28.74074074074075</v>
+        <v>28.740740740740748</v>
       </c>
       <c r="Y99" s="10" t="n">
         <v>43.00000000000001</v>
@@ -12253,22 +12253,22 @@
         <v>78.43453510436434</v>
       </c>
       <c r="AA99" s="10" t="n">
-        <v>9.484444444444447</v>
+        <v>1.4370370370370376</v>
       </c>
       <c r="AB99" s="10" t="n">
-        <v>14.62</v>
+        <v>39.56</v>
       </c>
       <c r="AC99" s="10" t="n">
-        <v>25.88339658444023</v>
+        <v>6.274762808349148</v>
       </c>
       <c r="AD99" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE99" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12306,22 +12306,22 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M100" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N100" s="8" t="inlineStr">
@@ -12345,25 +12345,25 @@
       </c>
       <c r="S100" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T100" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="U100" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V100" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>49.98784102888469</v>
+        <v>45.83476280834915</v>
       </c>
       <c r="X100" s="10" t="n">
-        <v>28.74074074074075</v>
+        <v>28.740740740740748</v>
       </c>
       <c r="Y100" s="10" t="n">
         <v>43.00000000000001</v>
@@ -12372,22 +12372,22 @@
         <v>78.43453510436434</v>
       </c>
       <c r="AA100" s="10" t="n">
-        <v>9.484444444444447</v>
+        <v>1.4370370370370376</v>
       </c>
       <c r="AB100" s="10" t="n">
-        <v>14.62</v>
+        <v>39.56</v>
       </c>
       <c r="AC100" s="10" t="n">
-        <v>25.88339658444023</v>
+        <v>6.274762808349148</v>
       </c>
       <c r="AD100" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE100" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12425,22 +12425,22 @@
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N101" s="8" t="inlineStr">
@@ -12464,25 +12464,25 @@
       </c>
       <c r="S101" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T101" s="10" t="n">
-        <v>50.00495378815151</v>
+        <v>45.698497308934336</v>
       </c>
       <c r="U101" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V101" s="10" t="n">
-        <v>50.00495378815151</v>
+        <v>45.698497308934336</v>
       </c>
       <c r="W101" s="10" t="n">
-        <v>50.00495378815151</v>
+        <v>45.698497308934336</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>28.40197693574959</v>
+        <v>28.40197693574958</v>
       </c>
       <c r="Y101" s="10" t="n">
         <v>42.8</v>
@@ -12491,22 +12491,22 @@
         <v>79.03121636167923</v>
       </c>
       <c r="AA101" s="10" t="n">
-        <v>9.372652388797365</v>
+        <v>1.420098846787479</v>
       </c>
       <c r="AB101" s="10" t="n">
-        <v>14.552</v>
+        <v>39.376</v>
       </c>
       <c r="AC101" s="10" t="n">
-        <v>26.08030139935414</v>
+        <v>6.322497308934338</v>
       </c>
       <c r="AD101" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE101" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12548,22 +12548,22 @@
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M102" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N102" s="8" t="inlineStr">
@@ -12593,49 +12593,49 @@
       </c>
       <c r="S102" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T102" s="10" t="n">
-        <v>50.0775982034346</v>
+        <v>45.527631079620505</v>
       </c>
       <c r="U102" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V102" s="10" t="n">
-        <v>50.0775982034346</v>
+        <v>45.527631079620505</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>50.0775982034346</v>
+        <v>45.527631079620505</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>28.664</v>
       </c>
       <c r="Y102" s="10" t="n">
-        <v>42.59999999999999</v>
+        <v>42.599999999999994</v>
       </c>
       <c r="Z102" s="10" t="n">
         <v>79.19538849525638</v>
       </c>
       <c r="AA102" s="10" t="n">
-        <v>9.45912</v>
+        <v>1.4332</v>
       </c>
       <c r="AB102" s="10" t="n">
-        <v>14.484</v>
+        <v>39.19199999999999</v>
       </c>
       <c r="AC102" s="10" t="n">
-        <v>26.1344782034346</v>
+        <v>6.33563107962051</v>
       </c>
       <c r="AD102" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE102" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12677,22 +12677,22 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>D · 吸引力偏弱</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>B · 加大买入区间</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>C · 基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N103" s="8" t="inlineStr">
@@ -12722,22 +12722,22 @@
       </c>
       <c r="S103" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T103" s="10" t="n">
-        <v>50.50662475175587</v>
+        <v>44.98381206103172</v>
       </c>
       <c r="U103" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V103" s="10" t="n">
-        <v>50.50662475175587</v>
+        <v>44.98381206103172</v>
       </c>
       <c r="W103" s="10" t="n">
-        <v>50.50662475175587</v>
+        <v>44.98381206103172</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>30.48</v>
@@ -12749,22 +12749,22 @@
         <v>79.29765076289658</v>
       </c>
       <c r="AA103" s="10" t="n">
-        <v>10.0584</v>
+        <v>1.524</v>
       </c>
       <c r="AB103" s="10" t="n">
-        <v>14.28</v>
+        <v>38.63999999999999</v>
       </c>
       <c r="AC103" s="10" t="n">
-        <v>26.16822475175587</v>
+        <v>6.343812061031726</v>
       </c>
       <c r="AD103" s="8" t="inlineStr">
         <is>
-          <t>参考评分；历史数据试算</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE103" s="8" t="inlineStr">
         <is>
-          <t>历史重算，不作为当时连续确认信号</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>
@@ -12806,22 +12806,22 @@
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t xml:space="preserve">D · 吸引力偏弱</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C · 指标得分一般</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t xml:space="preserve">A · 指标得分高</t>
         </is>
       </c>
       <c r="M104" s="12" t="inlineStr">
         <is>
-          <t>基础配置区间</t>
+          <t xml:space="preserve">C · 等待区间</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr">
@@ -12851,49 +12851,49 @@
       </c>
       <c r="S104" s="8" t="inlineStr">
         <is>
-          <t>dividend-weighted-v1-r3</t>
+          <t xml:space="preserve">dividend-two-factor-v2-r5</t>
         </is>
       </c>
       <c r="T104" s="10" t="n">
-        <v>51.49263568298537</v>
+        <v>46.89917956749593</v>
       </c>
       <c r="U104" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="V104" s="10" t="n">
-        <v>51.49263568298537</v>
+        <v>46.89917956749593</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>51.49263568298537</v>
+        <v>46.89917956749593</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>30.46521202140799</v>
+        <v>30.464</v>
       </c>
       <c r="Y104" s="10" t="n">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="Z104" s="10" t="n">
         <v>80.23974459369917</v>
       </c>
       <c r="AA104" s="10" t="n">
-        <v>10.05351996706464</v>
+        <v>1.5231999999999999</v>
       </c>
       <c r="AB104" s="10" t="n">
-        <v>14.96</v>
+        <v>40.48</v>
       </c>
       <c r="AC104" s="10" t="n">
-        <v>26.47911571592072</v>
+        <v>6.4191795674959335</v>
       </c>
       <c r="AD104" s="8" t="inlineStr">
         <is>
-          <t>参考评分</t>
+          <t xml:space="preserve">历史数据试算</t>
         </is>
       </c>
       <c r="AE104" s="8" t="inlineStr">
         <is>
-          <t>已建立 C 基准</t>
+          <t xml:space="preserve">历史重算，不作为当时连续确认信号</t>
         </is>
       </c>
     </row>

--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE108"/>
+  <dimension ref="A1:AE110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -515,12 +515,12 @@
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
     <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
     <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
     <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="25" customWidth="1" min="27" max="27"/>
     <col width="23" customWidth="1" min="28" max="28"/>
@@ -13252,11 +13252,11 @@
           <t>等待区间</t>
         </is>
       </c>
-      <c r="N108" s="3" t="inlineStr"/>
-      <c r="O108" s="4" t="inlineStr"/>
-      <c r="P108" s="4" t="inlineStr"/>
-      <c r="Q108" s="4" t="inlineStr"/>
-      <c r="R108" s="7" t="inlineStr"/>
+      <c r="N108" s="3" t="n"/>
+      <c r="O108" s="4" t="n"/>
+      <c r="P108" s="4" t="n"/>
+      <c r="Q108" s="4" t="n"/>
+      <c r="R108" s="7" t="n"/>
       <c r="S108" s="3" t="inlineStr">
         <is>
           <t>dividend-two-factor-v2-r5</t>
@@ -13276,14 +13276,14 @@
       <c r="W108" s="5" t="n">
         <v>46.5478077534548</v>
       </c>
-      <c r="X108" s="5" t="inlineStr"/>
+      <c r="X108" s="5" t="n"/>
       <c r="Y108" s="5" t="n">
         <v>43.59999999999999</v>
       </c>
       <c r="Z108" s="5" t="n">
         <v>80.44759691818516</v>
       </c>
-      <c r="AA108" s="5" t="inlineStr"/>
+      <c r="AA108" s="5" t="n"/>
       <c r="AB108" s="5" t="n">
         <v>40.11199999999999</v>
       </c>
@@ -13301,8 +13301,210 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>-0.4908490675315624</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>1.6412</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>2.5888</v>
+      </c>
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>等待区间</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="n"/>
+      <c r="O109" s="4" t="n"/>
+      <c r="P109" s="4" t="n"/>
+      <c r="Q109" s="4" t="n"/>
+      <c r="R109" s="7" t="n"/>
+      <c r="S109" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T109" s="5" t="n">
+        <v>47.4815247379966</v>
+      </c>
+      <c r="U109" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V109" s="5" t="n">
+        <v>47.4815247379966</v>
+      </c>
+      <c r="W109" s="5" t="n">
+        <v>47.4815247379966</v>
+      </c>
+      <c r="X109" s="5" t="n"/>
+      <c r="Y109" s="5" t="n">
+        <v>44.60000000000001</v>
+      </c>
+      <c r="Z109" s="5" t="n">
+        <v>80.61905922495735</v>
+      </c>
+      <c r="AA109" s="5" t="n"/>
+      <c r="AB109" s="5" t="n">
+        <v>41.03200000000001</v>
+      </c>
+      <c r="AC109" s="5" t="n">
+        <v>6.449524737996589</v>
+      </c>
+      <c r="AD109" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE109" s="3" t="inlineStr">
+        <is>
+          <t>已确认 C，策略维持</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>-2.160496061623995</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>1.6414</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>2.6586</v>
+      </c>
+      <c r="J110" s="6" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>观察区间</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr"/>
+      <c r="P110" s="4" t="inlineStr"/>
+      <c r="Q110" s="4" t="inlineStr"/>
+      <c r="R110" s="7" t="inlineStr"/>
+      <c r="S110" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T110" s="5" t="n">
+        <v>48.79661752162788</v>
+      </c>
+      <c r="U110" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V110" s="5" t="n">
+        <v>48.79661752162788</v>
+      </c>
+      <c r="W110" s="5" t="n">
+        <v>48.79661752162788</v>
+      </c>
+      <c r="X110" s="5" t="inlineStr"/>
+      <c r="Y110" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z110" s="5" t="n">
+        <v>80.95771902034848</v>
+      </c>
+      <c r="AA110" s="5" t="inlineStr"/>
+      <c r="AB110" s="5" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AC110" s="5" t="n">
+        <v>6.476617521627878</v>
+      </c>
+      <c r="AD110" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE110" s="3" t="inlineStr">
+        <is>
+          <t>策略调整已确认：B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE108"/>
+  <autoFilter ref="A1:AE110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE110"/>
+  <dimension ref="A1:AE111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13454,11 +13454,11 @@
           <t>观察区间</t>
         </is>
       </c>
-      <c r="N110" s="3" t="inlineStr"/>
-      <c r="O110" s="4" t="inlineStr"/>
-      <c r="P110" s="4" t="inlineStr"/>
-      <c r="Q110" s="4" t="inlineStr"/>
-      <c r="R110" s="7" t="inlineStr"/>
+      <c r="N110" s="3" t="n"/>
+      <c r="O110" s="4" t="n"/>
+      <c r="P110" s="4" t="n"/>
+      <c r="Q110" s="4" t="n"/>
+      <c r="R110" s="7" t="n"/>
       <c r="S110" s="3" t="inlineStr">
         <is>
           <t>dividend-two-factor-v2-r5</t>
@@ -13478,14 +13478,14 @@
       <c r="W110" s="5" t="n">
         <v>48.79661752162788</v>
       </c>
-      <c r="X110" s="5" t="inlineStr"/>
+      <c r="X110" s="5" t="n"/>
       <c r="Y110" s="5" t="n">
         <v>46</v>
       </c>
       <c r="Z110" s="5" t="n">
         <v>80.95771902034848</v>
       </c>
-      <c r="AA110" s="5" t="inlineStr"/>
+      <c r="AA110" s="5" t="n"/>
       <c r="AB110" s="5" t="n">
         <v>42.32</v>
       </c>
@@ -13503,8 +13503,109 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>-2.285923201668016</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>观察区间</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr"/>
+      <c r="O111" s="4" t="inlineStr"/>
+      <c r="P111" s="4" t="inlineStr"/>
+      <c r="Q111" s="4" t="inlineStr"/>
+      <c r="R111" s="7" t="inlineStr"/>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T111" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="U111" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V111" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="W111" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="X111" s="5" t="inlineStr"/>
+      <c r="Y111" s="5" t="n">
+        <v>46.19999999999999</v>
+      </c>
+      <c r="Z111" s="5" t="n">
+        <v>81.02439024390245</v>
+      </c>
+      <c r="AA111" s="5" t="inlineStr"/>
+      <c r="AB111" s="5" t="n">
+        <v>42.50399999999999</v>
+      </c>
+      <c r="AC111" s="5" t="n">
+        <v>6.481951219512196</v>
+      </c>
+      <c r="AD111" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE111" s="3" t="inlineStr">
+        <is>
+          <t>已确认 B，策略维持</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE110"/>
+  <autoFilter ref="A1:AE111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE111"/>
+  <dimension ref="A1:AE115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13555,11 +13555,11 @@
           <t>观察区间</t>
         </is>
       </c>
-      <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="4" t="inlineStr"/>
-      <c r="P111" s="4" t="inlineStr"/>
-      <c r="Q111" s="4" t="inlineStr"/>
-      <c r="R111" s="7" t="inlineStr"/>
+      <c r="N111" s="3" t="n"/>
+      <c r="O111" s="4" t="n"/>
+      <c r="P111" s="4" t="n"/>
+      <c r="Q111" s="4" t="n"/>
+      <c r="R111" s="7" t="n"/>
       <c r="S111" s="3" t="inlineStr">
         <is>
           <t>dividend-two-factor-v2-r5</t>
@@ -13579,14 +13579,14 @@
       <c r="W111" s="5" t="n">
         <v>48.98595121951219</v>
       </c>
-      <c r="X111" s="5" t="inlineStr"/>
+      <c r="X111" s="5" t="n"/>
       <c r="Y111" s="5" t="n">
         <v>46.19999999999999</v>
       </c>
       <c r="Z111" s="5" t="n">
         <v>81.02439024390245</v>
       </c>
-      <c r="AA111" s="5" t="inlineStr"/>
+      <c r="AA111" s="5" t="n"/>
       <c r="AB111" s="5" t="n">
         <v>42.50399999999999</v>
       </c>
@@ -13604,8 +13604,412 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>-2.285923201668016</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J112" s="6" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M112" s="7" t="inlineStr">
+        <is>
+          <t>观察区间</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="n"/>
+      <c r="O112" s="4" t="n"/>
+      <c r="P112" s="4" t="n"/>
+      <c r="Q112" s="4" t="n"/>
+      <c r="R112" s="7" t="n"/>
+      <c r="S112" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T112" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="U112" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V112" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="W112" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="X112" s="5" t="n"/>
+      <c r="Y112" s="5" t="n">
+        <v>46.19999999999999</v>
+      </c>
+      <c r="Z112" s="5" t="n">
+        <v>81.02439024390245</v>
+      </c>
+      <c r="AA112" s="5" t="n"/>
+      <c r="AB112" s="5" t="n">
+        <v>42.50399999999999</v>
+      </c>
+      <c r="AC112" s="5" t="n">
+        <v>6.481951219512196</v>
+      </c>
+      <c r="AD112" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE112" s="3" t="inlineStr">
+        <is>
+          <t>已确认 B，策略维持</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>-2.285923201668016</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J113" s="6" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
+          <t>观察区间</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="n"/>
+      <c r="O113" s="4" t="n"/>
+      <c r="P113" s="4" t="n"/>
+      <c r="Q113" s="4" t="n"/>
+      <c r="R113" s="7" t="n"/>
+      <c r="S113" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T113" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="U113" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V113" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="W113" s="5" t="n">
+        <v>48.98595121951219</v>
+      </c>
+      <c r="X113" s="5" t="n"/>
+      <c r="Y113" s="5" t="n">
+        <v>46.19999999999999</v>
+      </c>
+      <c r="Z113" s="5" t="n">
+        <v>81.02439024390245</v>
+      </c>
+      <c r="AA113" s="5" t="n"/>
+      <c r="AB113" s="5" t="n">
+        <v>42.50399999999999</v>
+      </c>
+      <c r="AC113" s="5" t="n">
+        <v>6.481951219512196</v>
+      </c>
+      <c r="AD113" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE113" s="3" t="inlineStr">
+        <is>
+          <t>已确认 B，策略维持</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>-1.087940171435187</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>1.6376</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>2.6124</v>
+      </c>
+      <c r="J114" s="6" t="inlineStr"/>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>等待区间</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="n"/>
+      <c r="O114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
+      <c r="Q114" s="4" t="n"/>
+      <c r="R114" s="7" t="n"/>
+      <c r="S114" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T114" s="5" t="n">
+        <v>47.8609672691744</v>
+      </c>
+      <c r="U114" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V114" s="5" t="n">
+        <v>47.8609672691744</v>
+      </c>
+      <c r="W114" s="5" t="n">
+        <v>47.8609672691744</v>
+      </c>
+      <c r="X114" s="5" t="n"/>
+      <c r="Y114" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z114" s="5" t="n">
+        <v>80.76209086468002</v>
+      </c>
+      <c r="AA114" s="5" t="n"/>
+      <c r="AB114" s="5" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AC114" s="5" t="n">
+        <v>6.460967269174401</v>
+      </c>
+      <c r="AD114" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE114" s="3" t="inlineStr">
+        <is>
+          <t>策略调整已确认：C</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>-0.4955548476775151</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>1.6258</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>2.604200000000001</v>
+      </c>
+      <c r="J115" s="6" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>等待区间</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr"/>
+      <c r="O115" s="4" t="inlineStr"/>
+      <c r="P115" s="4" t="inlineStr"/>
+      <c r="Q115" s="4" t="inlineStr"/>
+      <c r="R115" s="7" t="inlineStr"/>
+      <c r="S115" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T115" s="5" t="n">
+        <v>47.49714946487884</v>
+      </c>
+      <c r="U115" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V115" s="5" t="n">
+        <v>47.49714946487884</v>
+      </c>
+      <c r="W115" s="5" t="n">
+        <v>47.49714946487884</v>
+      </c>
+      <c r="X115" s="5" t="inlineStr"/>
+      <c r="Y115" s="5" t="n">
+        <v>44.60000000000001</v>
+      </c>
+      <c r="Z115" s="5" t="n">
+        <v>80.81436831098537</v>
+      </c>
+      <c r="AA115" s="5" t="inlineStr"/>
+      <c r="AB115" s="5" t="n">
+        <v>41.03200000000001</v>
+      </c>
+      <c r="AC115" s="5" t="n">
+        <v>6.46514946487883</v>
+      </c>
+      <c r="AD115" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE115" s="3" t="inlineStr">
+        <is>
+          <t>已确认 C，策略维持</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE111"/>
+  <autoFilter ref="A1:AE115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$AE$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE115"/>
+  <dimension ref="A1:AE118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13959,11 +13959,11 @@
           <t>等待区间</t>
         </is>
       </c>
-      <c r="N115" s="3" t="inlineStr"/>
-      <c r="O115" s="4" t="inlineStr"/>
-      <c r="P115" s="4" t="inlineStr"/>
-      <c r="Q115" s="4" t="inlineStr"/>
-      <c r="R115" s="7" t="inlineStr"/>
+      <c r="N115" s="3" t="n"/>
+      <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
+      <c r="Q115" s="4" t="n"/>
+      <c r="R115" s="7" t="n"/>
       <c r="S115" s="3" t="inlineStr">
         <is>
           <t>dividend-two-factor-v2-r5</t>
@@ -13983,14 +13983,14 @@
       <c r="W115" s="5" t="n">
         <v>47.49714946487884</v>
       </c>
-      <c r="X115" s="5" t="inlineStr"/>
+      <c r="X115" s="5" t="n"/>
       <c r="Y115" s="5" t="n">
         <v>44.60000000000001</v>
       </c>
       <c r="Z115" s="5" t="n">
         <v>80.81436831098537</v>
       </c>
-      <c r="AA115" s="5" t="inlineStr"/>
+      <c r="AA115" s="5" t="n"/>
       <c r="AB115" s="5" t="n">
         <v>41.03200000000001</v>
       </c>
@@ -14008,8 +14008,311 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>-0.4667771921695762</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>1.6345</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>2.5955</v>
+      </c>
+      <c r="J116" s="6" t="inlineStr"/>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>等待区间</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="n"/>
+      <c r="O116" s="4" t="n"/>
+      <c r="P116" s="4" t="n"/>
+      <c r="Q116" s="4" t="n"/>
+      <c r="R116" s="7" t="n"/>
+      <c r="S116" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T116" s="5" t="n">
+        <v>47.48828632609361</v>
+      </c>
+      <c r="U116" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V116" s="5" t="n">
+        <v>47.48828632609361</v>
+      </c>
+      <c r="W116" s="5" t="n">
+        <v>47.48828632609361</v>
+      </c>
+      <c r="X116" s="5" t="n"/>
+      <c r="Y116" s="5" t="n">
+        <v>44.60000000000001</v>
+      </c>
+      <c r="Z116" s="5" t="n">
+        <v>80.70357907617009</v>
+      </c>
+      <c r="AA116" s="5" t="n"/>
+      <c r="AB116" s="5" t="n">
+        <v>41.03200000000001</v>
+      </c>
+      <c r="AC116" s="5" t="n">
+        <v>6.456286326093607</v>
+      </c>
+      <c r="AD116" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE116" s="3" t="inlineStr">
+        <is>
+          <t>已确认 C，策略维持</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>0.3918466929225151</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>1.6233</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>2.5667</v>
+      </c>
+      <c r="J117" s="6" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>等待区间</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="n"/>
+      <c r="O117" s="4" t="n"/>
+      <c r="P117" s="4" t="n"/>
+      <c r="Q117" s="4" t="n"/>
+      <c r="R117" s="7" t="n"/>
+      <c r="S117" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T117" s="5" t="n">
+        <v>46.7479435717366</v>
+      </c>
+      <c r="U117" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V117" s="5" t="n">
+        <v>46.7479435717366</v>
+      </c>
+      <c r="W117" s="5" t="n">
+        <v>46.7479435717366</v>
+      </c>
+      <c r="X117" s="5" t="n"/>
+      <c r="Y117" s="5" t="n">
+        <v>43.80000000000001</v>
+      </c>
+      <c r="Z117" s="5" t="n">
+        <v>80.64929464670732</v>
+      </c>
+      <c r="AA117" s="5" t="n"/>
+      <c r="AB117" s="5" t="n">
+        <v>40.29600000000001</v>
+      </c>
+      <c r="AC117" s="5" t="n">
+        <v>6.451943571736585</v>
+      </c>
+      <c r="AD117" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE117" s="3" t="inlineStr">
+        <is>
+          <t>已确认 C，策略维持</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>1.218616066257394</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>2.580000000000001</v>
+      </c>
+      <c r="J118" s="6" t="inlineStr"/>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M118" s="7" t="inlineStr">
+        <is>
+          <t>等待区间</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr"/>
+      <c r="P118" s="4" t="inlineStr"/>
+      <c r="Q118" s="4" t="inlineStr"/>
+      <c r="R118" s="7" t="inlineStr"/>
+      <c r="S118" s="3" t="inlineStr">
+        <is>
+          <t>dividend-two-factor-v2-r5</t>
+        </is>
+      </c>
+      <c r="T118" s="5" t="n">
+        <v>47.47272727272728</v>
+      </c>
+      <c r="U118" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V118" s="5" t="n">
+        <v>47.47272727272728</v>
+      </c>
+      <c r="W118" s="5" t="n">
+        <v>47.47272727272728</v>
+      </c>
+      <c r="X118" s="5" t="inlineStr"/>
+      <c r="Y118" s="5" t="n">
+        <v>44.60000000000001</v>
+      </c>
+      <c r="Z118" s="5" t="n">
+        <v>80.50909090909092</v>
+      </c>
+      <c r="AA118" s="5" t="inlineStr"/>
+      <c r="AB118" s="5" t="n">
+        <v>41.03200000000001</v>
+      </c>
+      <c r="AC118" s="5" t="n">
+        <v>6.440727272727274</v>
+      </c>
+      <c r="AD118" s="3" t="inlineStr">
+        <is>
+          <t>数据完整</t>
+        </is>
+      </c>
+      <c r="AE118" s="3" t="inlineStr">
+        <is>
+          <t>已确认 C，策略维持</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE115"/>
+  <autoFilter ref="A1:AE118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>